--- a/trade.xlsx
+++ b/trade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\App\MyPython\PortFolioManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA3DDE4-B583-4FB8-AB65-C31601A553D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0CA088-029A-4A8A-8914-30F458A84D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17377" yWindow="-98" windowWidth="17475" windowHeight="10276" tabRatio="913" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="913" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="22" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="176">
   <si>
     <t>LUPIN</t>
   </si>
@@ -894,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F10F07C-C431-47C0-A311-5E8452401DEC}">
-  <dimension ref="A1:M623"/>
+  <dimension ref="A1:M624"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.90625" bestFit="1" customWidth="1"/>
@@ -2607,22 +2607,22 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C86" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D86" s="1">
-        <v>337.8</v>
+        <v>0</v>
       </c>
       <c r="E86" s="2">
-        <v>43819</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>120</v>
+        <v>45577</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -2633,13 +2633,13 @@
         <v>113</v>
       </c>
       <c r="C87" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D87" s="1">
-        <v>337</v>
+        <v>337.8</v>
       </c>
       <c r="E87" s="2">
-        <v>43832</v>
+        <v>43819</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>120</v>
@@ -2653,31 +2653,30 @@
         <v>113</v>
       </c>
       <c r="C88" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D88" s="1">
-        <v>318.8</v>
+        <v>337</v>
       </c>
       <c r="E88" s="2">
-        <v>43859</v>
+        <v>43832</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="M88" s="3"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C89" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="D89" s="1">
-        <v>41.75</v>
+        <v>318.8</v>
       </c>
       <c r="E89" s="2">
         <v>43859</v>
@@ -2685,22 +2684,23 @@
       <c r="F89" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="M89" s="3"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C90" s="1">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="D90" s="1">
-        <v>330.5</v>
+        <v>41.75</v>
       </c>
       <c r="E90" s="2">
-        <v>43875</v>
+        <v>43859</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>120</v>
@@ -2708,19 +2708,19 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C91" s="1">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D91" s="1">
-        <v>541.35</v>
+        <v>330.5</v>
       </c>
       <c r="E91" s="2">
-        <v>43880</v>
+        <v>43875</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>120</v>
@@ -2728,16 +2728,16 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C92" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D92" s="1">
-        <v>1502</v>
+        <v>541.35</v>
       </c>
       <c r="E92" s="2">
         <v>43880</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C93" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D93" s="1">
-        <v>475.3</v>
+        <v>1502</v>
       </c>
       <c r="E93" s="2">
         <v>43880</v>
@@ -2768,16 +2768,16 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C94" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D94" s="1">
-        <v>544.20000000000005</v>
+        <v>475.3</v>
       </c>
       <c r="E94" s="2">
         <v>43880</v>
@@ -2788,16 +2788,16 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C95" s="1">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="D95" s="1">
-        <v>84.4</v>
+        <v>544.20000000000005</v>
       </c>
       <c r="E95" s="2">
         <v>43880</v>
@@ -2808,16 +2808,16 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C96" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D96" s="1">
-        <v>148.69999999999999</v>
+        <v>84.4</v>
       </c>
       <c r="E96" s="2">
         <v>43880</v>
@@ -2828,16 +2828,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C97" s="1">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D97" s="1">
-        <v>1280.25</v>
+        <v>148.69999999999999</v>
       </c>
       <c r="E97" s="2">
         <v>43880</v>
@@ -2848,16 +2848,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C98" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D98" s="1">
-        <v>164.65</v>
+        <v>1280.25</v>
       </c>
       <c r="E98" s="2">
         <v>43880</v>
@@ -2868,16 +2868,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C99" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D99" s="1">
-        <v>119.95</v>
+        <v>164.65</v>
       </c>
       <c r="E99" s="2">
         <v>43880</v>
@@ -2888,16 +2888,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C100" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D100" s="1">
-        <v>479.1</v>
+        <v>119.95</v>
       </c>
       <c r="E100" s="2">
         <v>43880</v>
@@ -2934,7 +2934,7 @@
         <v>113</v>
       </c>
       <c r="C102" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D102" s="1">
         <v>479.1</v>
@@ -2948,16 +2948,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C103" s="1">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D103" s="1">
-        <v>158.25</v>
+        <v>479.1</v>
       </c>
       <c r="E103" s="2">
         <v>43880</v>
@@ -2968,16 +2968,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C104" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D104" s="1">
-        <v>320.05</v>
+        <v>158.25</v>
       </c>
       <c r="E104" s="2">
         <v>43880</v>
@@ -2988,16 +2988,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C105" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D105" s="1">
-        <v>3353.45</v>
+        <v>320.05</v>
       </c>
       <c r="E105" s="2">
         <v>43880</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>113</v>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="1">
-        <v>1281.2</v>
+        <v>3353.45</v>
       </c>
       <c r="E106" s="2">
         <v>43880</v>
@@ -3028,19 +3028,19 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C107" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D107" s="1">
-        <v>1404</v>
+        <v>1281.2</v>
       </c>
       <c r="E107" s="2">
-        <v>43887</v>
+        <v>43880</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>120</v>
@@ -3048,16 +3048,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C108" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D108" s="1">
-        <v>527</v>
+        <v>1404</v>
       </c>
       <c r="E108" s="2">
         <v>43887</v>
@@ -3068,16 +3068,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C109" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D109" s="1">
-        <v>85.9</v>
+        <v>527</v>
       </c>
       <c r="E109" s="2">
         <v>43887</v>
@@ -3088,16 +3088,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C110" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D110" s="1">
-        <v>155.5</v>
+        <v>85.9</v>
       </c>
       <c r="E110" s="2">
         <v>43887</v>
@@ -3108,16 +3108,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C111" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D111" s="1">
-        <v>146</v>
+        <v>155.5</v>
       </c>
       <c r="E111" s="2">
         <v>43887</v>
@@ -3128,16 +3128,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C112" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D112" s="1">
-        <v>152.30000000000001</v>
+        <v>146</v>
       </c>
       <c r="E112" s="2">
         <v>43887</v>
@@ -3148,16 +3148,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C113" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D113" s="1">
-        <v>109.7</v>
+        <v>152.30000000000001</v>
       </c>
       <c r="E113" s="2">
         <v>43887</v>
@@ -3168,16 +3168,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C114" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D114" s="1">
-        <v>535</v>
+        <v>109.7</v>
       </c>
       <c r="E114" s="2">
         <v>43887</v>
@@ -3188,16 +3188,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C115" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D115" s="1">
-        <v>350</v>
+        <v>535</v>
       </c>
       <c r="E115" s="2">
         <v>43887</v>
@@ -3208,16 +3208,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C116" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D116" s="1">
-        <v>429.8</v>
+        <v>350</v>
       </c>
       <c r="E116" s="2">
         <v>43887</v>
@@ -3228,16 +3228,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C117" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D117" s="1">
-        <v>448</v>
+        <v>429.8</v>
       </c>
       <c r="E117" s="2">
         <v>43887</v>
@@ -3248,16 +3248,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C118" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D118" s="1">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="E118" s="2">
         <v>43887</v>
@@ -3268,16 +3268,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C119" s="1">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D119" s="1">
-        <v>173.75</v>
+        <v>482</v>
       </c>
       <c r="E119" s="2">
         <v>43887</v>
@@ -3288,16 +3288,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C120" s="1">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D120" s="1">
-        <v>562</v>
+        <v>173.75</v>
       </c>
       <c r="E120" s="2">
         <v>43887</v>
@@ -3308,16 +3308,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C121" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D121" s="1">
-        <v>897</v>
+        <v>562</v>
       </c>
       <c r="E121" s="2">
         <v>43887</v>
@@ -3328,16 +3328,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C122" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D122" s="1">
-        <v>1210</v>
+        <v>897</v>
       </c>
       <c r="E122" s="2">
         <v>43887</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>113</v>
@@ -3357,10 +3357,10 @@
         <v>2</v>
       </c>
       <c r="D123" s="1">
-        <v>2060</v>
+        <v>1210</v>
       </c>
       <c r="E123" s="2">
-        <v>43889</v>
+        <v>43887</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>120</v>
@@ -3368,16 +3368,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C124" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D124" s="1">
-        <v>1220</v>
+        <v>2060</v>
       </c>
       <c r="E124" s="2">
         <v>43889</v>
@@ -3388,16 +3388,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C125" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D125" s="1">
-        <v>128.69999999999999</v>
+        <v>1220</v>
       </c>
       <c r="E125" s="2">
         <v>43889</v>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>113</v>
@@ -3417,7 +3417,7 @@
         <v>10</v>
       </c>
       <c r="D126" s="1">
-        <v>390.4</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="E126" s="2">
         <v>43889</v>
@@ -3434,10 +3434,10 @@
         <v>113</v>
       </c>
       <c r="C127" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D127" s="1">
-        <v>390.2</v>
+        <v>390.4</v>
       </c>
       <c r="E127" s="2">
         <v>43889</v>
@@ -3448,19 +3448,19 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C128" s="1">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="D128" s="1">
-        <v>221.1</v>
+        <v>390.2</v>
       </c>
       <c r="E128" s="2">
-        <v>43907</v>
+        <v>43889</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>120</v>
@@ -3468,16 +3468,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C129" s="1">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="D129" s="1">
-        <v>62.35</v>
+        <v>221.1</v>
       </c>
       <c r="E129" s="2">
         <v>43907</v>
@@ -3488,16 +3488,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C130" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D130" s="1">
-        <v>366.65</v>
+        <v>62.35</v>
       </c>
       <c r="E130" s="2">
         <v>43907</v>
@@ -3508,16 +3508,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C131" s="1">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="D131" s="1">
-        <v>59.15</v>
+        <v>366.65</v>
       </c>
       <c r="E131" s="2">
         <v>43907</v>
@@ -3528,16 +3528,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C132" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="D132" s="1">
-        <v>2429.65</v>
+        <v>59.15</v>
       </c>
       <c r="E132" s="2">
         <v>43907</v>
@@ -3548,19 +3548,19 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C133" s="1">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="D133" s="1">
-        <v>65.150000000000006</v>
+        <v>2429.65</v>
       </c>
       <c r="E133" s="2">
-        <v>43908</v>
+        <v>43907</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>120</v>
@@ -3571,13 +3571,13 @@
         <v>46</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C134" s="1">
         <v>300</v>
       </c>
       <c r="D134" s="1">
-        <v>62.15</v>
+        <v>65.150000000000006</v>
       </c>
       <c r="E134" s="2">
         <v>43908</v>
@@ -3588,19 +3588,19 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C135" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="D135" s="1">
-        <v>3197</v>
+        <v>62.15</v>
       </c>
       <c r="E135" s="2">
-        <v>43909</v>
+        <v>43908</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>120</v>
@@ -3608,19 +3608,19 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C136" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D136" s="1">
-        <v>334.9</v>
+        <v>3197</v>
       </c>
       <c r="E136" s="2">
-        <v>43913</v>
+        <v>43909</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>120</v>
@@ -3628,19 +3628,19 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C137" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D137" s="1">
-        <v>574.45000000000005</v>
+        <v>334.9</v>
       </c>
       <c r="E137" s="2">
-        <v>43914</v>
+        <v>43913</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>120</v>
@@ -3648,16 +3648,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C138" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D138" s="1">
-        <v>910.6</v>
+        <v>574.45000000000005</v>
       </c>
       <c r="E138" s="2">
         <v>43914</v>
@@ -3674,7 +3674,7 @@
         <v>117</v>
       </c>
       <c r="C139" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D139" s="1">
         <v>910.6</v>
@@ -3688,16 +3688,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C140" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D140" s="1">
-        <v>854.2</v>
+        <v>910.6</v>
       </c>
       <c r="E140" s="2">
         <v>43914</v>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>117</v>
@@ -3717,7 +3717,7 @@
         <v>4</v>
       </c>
       <c r="D141" s="1">
-        <v>356.95</v>
+        <v>854.2</v>
       </c>
       <c r="E141" s="2">
         <v>43914</v>
@@ -3728,16 +3728,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C142" s="1">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D142" s="1">
-        <v>129.19999999999999</v>
+        <v>356.95</v>
       </c>
       <c r="E142" s="2">
         <v>43914</v>
@@ -3748,16 +3748,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C143" s="1">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="D143" s="1">
-        <v>407.6</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="E143" s="2">
         <v>43914</v>
@@ -3774,7 +3774,7 @@
         <v>113</v>
       </c>
       <c r="C144" s="1">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="D144" s="1">
         <v>407.6</v>
@@ -3791,13 +3791,13 @@
         <v>71</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C145" s="1">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="D145" s="1">
-        <v>403.3</v>
+        <v>407.6</v>
       </c>
       <c r="E145" s="2">
         <v>43914</v>
@@ -3814,7 +3814,7 @@
         <v>117</v>
       </c>
       <c r="C146" s="1">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="D146" s="1">
         <v>403.3</v>
@@ -3828,19 +3828,19 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C147" s="1">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="D147" s="1">
-        <v>310.14999999999998</v>
+        <v>403.3</v>
       </c>
       <c r="E147" s="2">
-        <v>43915</v>
+        <v>43914</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>120</v>
@@ -3848,16 +3848,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C148" s="1">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D148" s="1">
-        <v>236.35</v>
+        <v>310.14999999999998</v>
       </c>
       <c r="E148" s="2">
         <v>43915</v>
@@ -3868,16 +3868,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C149" s="1">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D149" s="1">
-        <v>768.25</v>
+        <v>236.35</v>
       </c>
       <c r="E149" s="2">
         <v>43915</v>
@@ -3888,19 +3888,19 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C150" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D150" s="1">
-        <v>739.2</v>
+        <v>768.25</v>
       </c>
       <c r="E150" s="2">
-        <v>43921</v>
+        <v>43915</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>120</v>
@@ -3934,7 +3934,7 @@
         <v>113</v>
       </c>
       <c r="C152" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D152" s="1">
         <v>739.2</v>
@@ -3948,19 +3948,19 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C153" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D153" s="1">
-        <v>2185</v>
+        <v>739.2</v>
       </c>
       <c r="E153" s="2">
-        <v>43922</v>
+        <v>43921</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>120</v>
@@ -3968,19 +3968,19 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C154" s="1">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D154" s="1">
-        <v>313</v>
+        <v>2185</v>
       </c>
       <c r="E154" s="2">
-        <v>43928</v>
+        <v>43922</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>120</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>113</v>
@@ -3997,10 +3997,10 @@
         <v>50</v>
       </c>
       <c r="D155" s="1">
-        <v>157.19999999999999</v>
+        <v>313</v>
       </c>
       <c r="E155" s="2">
-        <v>43930</v>
+        <v>43928</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>120</v>
@@ -4008,16 +4008,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C156" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D156" s="1">
-        <v>339.95</v>
+        <v>157.19999999999999</v>
       </c>
       <c r="E156" s="2">
         <v>43930</v>
@@ -4028,16 +4028,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C157" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D157" s="1">
-        <v>355.25</v>
+        <v>339.95</v>
       </c>
       <c r="E157" s="2">
         <v>43930</v>
@@ -4048,16 +4048,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C158" s="1">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="D158" s="1">
-        <v>408.5</v>
+        <v>355.25</v>
       </c>
       <c r="E158" s="2">
         <v>43930</v>
@@ -4068,19 +4068,19 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C159" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="D159" s="1">
-        <v>74.7</v>
+        <v>408.5</v>
       </c>
       <c r="E159" s="2">
-        <v>43937</v>
+        <v>43930</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>120</v>
@@ -4088,16 +4088,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C160" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="D160" s="1">
-        <v>1142.8</v>
+        <v>74.7</v>
       </c>
       <c r="E160" s="2">
         <v>43937</v>
@@ -4108,16 +4108,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C161" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D161" s="1">
-        <v>284.39999999999998</v>
+        <v>1142.8</v>
       </c>
       <c r="E161" s="2">
         <v>43937</v>
@@ -4134,7 +4134,7 @@
         <v>113</v>
       </c>
       <c r="C162" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D162" s="1">
         <v>284.39999999999998</v>
@@ -4148,16 +4148,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C163" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D163" s="1">
-        <v>350.1</v>
+        <v>284.39999999999998</v>
       </c>
       <c r="E163" s="2">
         <v>43937</v>
@@ -4168,16 +4168,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C164" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D164" s="1">
-        <v>325.39999999999998</v>
+        <v>350.1</v>
       </c>
       <c r="E164" s="2">
         <v>43937</v>
@@ -4188,16 +4188,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C165" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D165" s="1">
-        <v>118.55</v>
+        <v>325.39999999999998</v>
       </c>
       <c r="E165" s="2">
         <v>43937</v>
@@ -4208,16 +4208,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C166" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D166" s="1">
-        <v>2481.85</v>
+        <v>118.55</v>
       </c>
       <c r="E166" s="2">
         <v>43937</v>
@@ -4228,16 +4228,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C167" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D167" s="1">
-        <v>255.25</v>
+        <v>2481.85</v>
       </c>
       <c r="E167" s="2">
         <v>43937</v>
@@ -4274,7 +4274,7 @@
         <v>113</v>
       </c>
       <c r="C169" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D169" s="1">
         <v>255.25</v>
@@ -4288,7 +4288,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>113</v>
@@ -4297,7 +4297,7 @@
         <v>4</v>
       </c>
       <c r="D170" s="1">
-        <v>931.85</v>
+        <v>255.25</v>
       </c>
       <c r="E170" s="2">
         <v>43937</v>
@@ -4308,16 +4308,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C171" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D171" s="1">
-        <v>60.1</v>
+        <v>931.85</v>
       </c>
       <c r="E171" s="2">
         <v>43937</v>
@@ -4328,19 +4328,19 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C172" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D172" s="1">
-        <v>1130.8499999999999</v>
+        <v>60.1</v>
       </c>
       <c r="E172" s="2">
-        <v>43942</v>
+        <v>43937</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>120</v>
@@ -4348,16 +4348,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C173" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D173" s="1">
-        <v>1740.6</v>
+        <v>1130.8499999999999</v>
       </c>
       <c r="E173" s="2">
         <v>43942</v>
@@ -4368,16 +4368,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C174" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D174" s="1">
-        <v>633.70000000000005</v>
+        <v>1740.6</v>
       </c>
       <c r="E174" s="2">
         <v>43942</v>
@@ -4388,16 +4388,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C175" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D175" s="1">
-        <v>68.400000000000006</v>
+        <v>633.70000000000005</v>
       </c>
       <c r="E175" s="2">
         <v>43942</v>
@@ -4408,16 +4408,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C176" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D176" s="1">
-        <v>668.75</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="E176" s="2">
         <v>43942</v>
@@ -4428,16 +4428,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C177" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D177" s="1">
-        <v>874</v>
+        <v>668.75</v>
       </c>
       <c r="E177" s="2">
         <v>43942</v>
@@ -4448,16 +4448,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C178" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D178" s="1">
-        <v>99.15</v>
+        <v>874</v>
       </c>
       <c r="E178" s="2">
         <v>43942</v>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>113</v>
@@ -4477,7 +4477,7 @@
         <v>25</v>
       </c>
       <c r="D179" s="1">
-        <v>179.85</v>
+        <v>99.15</v>
       </c>
       <c r="E179" s="2">
         <v>43942</v>
@@ -4488,16 +4488,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C180" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D180" s="1">
-        <v>4067.1</v>
+        <v>179.85</v>
       </c>
       <c r="E180" s="2">
         <v>43942</v>
@@ -4508,16 +4508,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C181" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D181" s="1">
-        <v>452.3</v>
+        <v>4067.1</v>
       </c>
       <c r="E181" s="2">
         <v>43942</v>
@@ -4528,16 +4528,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C182" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D182" s="1">
-        <v>266.2</v>
+        <v>452.3</v>
       </c>
       <c r="E182" s="2">
         <v>43942</v>
@@ -4548,16 +4548,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C183" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D183" s="1">
-        <v>495.1</v>
+        <v>266.2</v>
       </c>
       <c r="E183" s="2">
         <v>43942</v>
@@ -4568,7 +4568,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>113</v>
@@ -4577,10 +4577,10 @@
         <v>7</v>
       </c>
       <c r="D184" s="1">
-        <v>484.75</v>
+        <v>495.1</v>
       </c>
       <c r="E184" s="2">
-        <v>43945</v>
+        <v>43942</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>120</v>
@@ -4594,7 +4594,7 @@
         <v>113</v>
       </c>
       <c r="C185" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D185" s="1">
         <v>484.75</v>
@@ -4608,16 +4608,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C186" s="1">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D186" s="1">
-        <v>404.55</v>
+        <v>484.75</v>
       </c>
       <c r="E186" s="2">
         <v>43945</v>
@@ -4628,16 +4628,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C187" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D187" s="1">
-        <v>217</v>
+        <v>404.55</v>
       </c>
       <c r="E187" s="2">
         <v>43945</v>
@@ -4648,19 +4648,19 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C188" s="1">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D188" s="1">
-        <v>45.1</v>
+        <v>217</v>
       </c>
       <c r="E188" s="2">
-        <v>43949</v>
+        <v>43945</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>120</v>
@@ -4668,16 +4668,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C189" s="1">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D189" s="1">
-        <v>68.5</v>
+        <v>45.1</v>
       </c>
       <c r="E189" s="2">
         <v>43949</v>
@@ -4688,19 +4688,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C190" s="1">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D190" s="1">
-        <v>1974.45</v>
+        <v>68.5</v>
       </c>
       <c r="E190" s="2">
-        <v>43950</v>
+        <v>43949</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>120</v>
@@ -4708,16 +4708,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C191" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D191" s="1">
-        <v>477.35</v>
+        <v>1974.45</v>
       </c>
       <c r="E191" s="2">
         <v>43950</v>
@@ -4728,16 +4728,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C192" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D192" s="1">
-        <v>2274.9</v>
+        <v>477.35</v>
       </c>
       <c r="E192" s="2">
         <v>43950</v>
@@ -4748,16 +4748,16 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C193" s="1">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="D193" s="1">
-        <v>108.6</v>
+        <v>2274.9</v>
       </c>
       <c r="E193" s="2">
         <v>43950</v>
@@ -4774,7 +4774,7 @@
         <v>113</v>
       </c>
       <c r="C194" s="1">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D194" s="1">
         <v>108.6</v>
@@ -4788,19 +4788,19 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C195" s="1">
         <v>10</v>
       </c>
       <c r="D195" s="1">
-        <v>1100.0999999999999</v>
+        <v>108.6</v>
       </c>
       <c r="E195" s="2">
-        <v>43951</v>
+        <v>43950</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>120</v>
@@ -4808,16 +4808,16 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C196" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D196" s="1">
-        <v>4572</v>
+        <v>1100.0999999999999</v>
       </c>
       <c r="E196" s="2">
         <v>43951</v>
@@ -4828,16 +4828,16 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C197" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D197" s="1">
-        <v>410.25</v>
+        <v>4572</v>
       </c>
       <c r="E197" s="2">
         <v>43951</v>
@@ -4848,16 +4848,16 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C198" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D198" s="1">
-        <v>1351.95</v>
+        <v>410.25</v>
       </c>
       <c r="E198" s="2">
         <v>43951</v>
@@ -4868,16 +4868,16 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C199" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="D199" s="1">
-        <v>88.35</v>
+        <v>1351.95</v>
       </c>
       <c r="E199" s="2">
         <v>43951</v>
@@ -4888,19 +4888,19 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C200" s="1">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D200" s="1">
-        <v>329.85</v>
+        <v>88.35</v>
       </c>
       <c r="E200" s="2">
-        <v>43955</v>
+        <v>43951</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>120</v>
@@ -4908,16 +4908,16 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C201" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D201" s="1">
-        <v>210.9</v>
+        <v>329.85</v>
       </c>
       <c r="E201" s="2">
         <v>43955</v>
@@ -4928,16 +4928,16 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C202" s="1">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="D202" s="1">
-        <v>851</v>
+        <v>210.9</v>
       </c>
       <c r="E202" s="2">
         <v>43955</v>
@@ -4948,16 +4948,16 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C203" s="1">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="D203" s="1">
-        <v>115.5</v>
+        <v>851</v>
       </c>
       <c r="E203" s="2">
         <v>43955</v>
@@ -4968,16 +4968,16 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C204" s="1">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="D204" s="1">
-        <v>57.75</v>
+        <v>115.5</v>
       </c>
       <c r="E204" s="2">
         <v>43955</v>
@@ -4994,7 +4994,7 @@
         <v>117</v>
       </c>
       <c r="C205" s="1">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="D205" s="1">
         <v>57.75</v>
@@ -5008,16 +5008,16 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C206" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D206" s="1">
-        <v>93</v>
+        <v>57.75</v>
       </c>
       <c r="E206" s="2">
         <v>43955</v>
@@ -5028,16 +5028,16 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C207" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D207" s="1">
-        <v>272.75</v>
+        <v>93</v>
       </c>
       <c r="E207" s="2">
         <v>43955</v>
@@ -5048,19 +5048,19 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C208" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D208" s="1">
-        <v>665.8</v>
+        <v>272.75</v>
       </c>
       <c r="E208" s="2">
-        <v>43958</v>
+        <v>43955</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>120</v>
@@ -5068,16 +5068,16 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C209" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D209" s="1">
-        <v>1892.65</v>
+        <v>665.8</v>
       </c>
       <c r="E209" s="2">
         <v>43958</v>
@@ -5088,16 +5088,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C210" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D210" s="1">
-        <v>468.2</v>
+        <v>1892.65</v>
       </c>
       <c r="E210" s="2">
         <v>43958</v>
@@ -5108,16 +5108,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C211" s="1">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D211" s="1">
-        <v>168.75</v>
+        <v>468.2</v>
       </c>
       <c r="E211" s="2">
         <v>43958</v>
@@ -5134,10 +5134,10 @@
         <v>117</v>
       </c>
       <c r="C212" s="1">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D212" s="1">
-        <v>168.8</v>
+        <v>168.75</v>
       </c>
       <c r="E212" s="2">
         <v>43958</v>
@@ -5148,19 +5148,19 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C213" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D213" s="1">
-        <v>401.85</v>
+        <v>168.8</v>
       </c>
       <c r="E213" s="2">
-        <v>43965</v>
+        <v>43958</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>120</v>
@@ -5168,16 +5168,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C214" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D214" s="1">
-        <v>872.4</v>
+        <v>401.85</v>
       </c>
       <c r="E214" s="2">
         <v>43965</v>
@@ -5188,19 +5188,19 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C215" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D215" s="1">
-        <v>165.05</v>
+        <v>872.4</v>
       </c>
       <c r="E215" s="2">
-        <v>43969</v>
+        <v>43965</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>120</v>
@@ -5234,7 +5234,7 @@
         <v>117</v>
       </c>
       <c r="C217" s="1">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D217" s="1">
         <v>165.05</v>
@@ -5248,19 +5248,19 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C218" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D218" s="1">
-        <v>587</v>
+        <v>165.05</v>
       </c>
       <c r="E218" s="2">
-        <v>43970</v>
+        <v>43969</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>120</v>
@@ -5268,16 +5268,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C219" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D219" s="1">
-        <v>229.45</v>
+        <v>587</v>
       </c>
       <c r="E219" s="2">
         <v>43970</v>
@@ -5288,16 +5288,16 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C220" s="1">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D220" s="1">
-        <v>537.25</v>
+        <v>229.45</v>
       </c>
       <c r="E220" s="2">
         <v>43970</v>
@@ -5308,16 +5308,16 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C221" s="1">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="D221" s="1">
-        <v>68.3</v>
+        <v>537.25</v>
       </c>
       <c r="E221" s="2">
         <v>43970</v>
@@ -5328,16 +5328,16 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C222" s="1">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="D222" s="1">
-        <v>816.45</v>
+        <v>68.3</v>
       </c>
       <c r="E222" s="2">
         <v>43970</v>
@@ -5354,7 +5354,7 @@
         <v>117</v>
       </c>
       <c r="C223" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D223" s="1">
         <v>816.45</v>
@@ -5374,7 +5374,7 @@
         <v>117</v>
       </c>
       <c r="C224" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D224" s="1">
         <v>816.45</v>
@@ -5388,16 +5388,16 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C225" s="1">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D225" s="1">
-        <v>299.85000000000002</v>
+        <v>816.45</v>
       </c>
       <c r="E225" s="2">
         <v>43970</v>
@@ -5408,16 +5408,16 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C226" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D226" s="1">
-        <v>104</v>
+        <v>299.85000000000002</v>
       </c>
       <c r="E226" s="2">
         <v>43970</v>
@@ -5428,16 +5428,16 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C227" s="1">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D227" s="1">
-        <v>472.85</v>
+        <v>104</v>
       </c>
       <c r="E227" s="2">
         <v>43970</v>
@@ -5448,16 +5448,16 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C228" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D228" s="1">
-        <v>2082.5</v>
+        <v>472.85</v>
       </c>
       <c r="E228" s="2">
         <v>43970</v>
@@ -5468,16 +5468,16 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C229" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D229" s="1">
-        <v>894.05</v>
+        <v>2082.5</v>
       </c>
       <c r="E229" s="2">
         <v>43970</v>
@@ -5488,16 +5488,16 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C230" s="1">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D230" s="1">
-        <v>231.25</v>
+        <v>894.05</v>
       </c>
       <c r="E230" s="2">
         <v>43970</v>
@@ -5514,10 +5514,10 @@
         <v>117</v>
       </c>
       <c r="C231" s="1">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D231" s="1">
-        <v>231.2</v>
+        <v>231.25</v>
       </c>
       <c r="E231" s="2">
         <v>43970</v>
@@ -5528,16 +5528,16 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C232" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D232" s="1">
-        <v>703.1</v>
+        <v>231.2</v>
       </c>
       <c r="E232" s="2">
         <v>43970</v>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>117</v>
@@ -5557,7 +5557,7 @@
         <v>5</v>
       </c>
       <c r="D233" s="1">
-        <v>1976.4</v>
+        <v>703.1</v>
       </c>
       <c r="E233" s="2">
         <v>43970</v>
@@ -5568,19 +5568,19 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C234" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D234" s="1">
-        <v>460.9</v>
+        <v>1976.4</v>
       </c>
       <c r="E234" s="2">
-        <v>43977</v>
+        <v>43970</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>120</v>
@@ -5588,16 +5588,16 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C235" s="1">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="D235" s="1">
-        <v>35.950000000000003</v>
+        <v>460.9</v>
       </c>
       <c r="E235" s="2">
         <v>43977</v>
@@ -5608,19 +5608,19 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C236" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D236" s="1">
-        <v>87.15</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="E236" s="2">
-        <v>43979</v>
+        <v>43977</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>120</v>
@@ -5628,16 +5628,16 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C237" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="D237" s="1">
-        <v>26.9</v>
+        <v>87.15</v>
       </c>
       <c r="E237" s="2">
         <v>43979</v>
@@ -5648,19 +5648,19 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C238" s="1">
-        <v>3500</v>
+        <v>400</v>
       </c>
       <c r="D238" s="1">
-        <v>8.5</v>
+        <v>26.9</v>
       </c>
       <c r="E238" s="2">
-        <v>44033</v>
+        <v>43979</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>120</v>
@@ -5668,16 +5668,16 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C239" s="1">
-        <v>41</v>
+        <v>3500</v>
       </c>
       <c r="D239" s="1">
-        <v>230.95</v>
+        <v>8.5</v>
       </c>
       <c r="E239" s="2">
         <v>44033</v>
@@ -5688,19 +5688,19 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C240" s="1">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D240" s="1">
-        <v>429.7</v>
+        <v>230.95</v>
       </c>
       <c r="E240" s="2">
-        <v>44098</v>
+        <v>44033</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>120</v>
@@ -5714,10 +5714,10 @@
         <v>113</v>
       </c>
       <c r="C241" s="1">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D241" s="1">
-        <v>429.6</v>
+        <v>429.7</v>
       </c>
       <c r="E241" s="2">
         <v>44098</v>
@@ -5728,16 +5728,16 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C242" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D242" s="1">
-        <v>391.65</v>
+        <v>429.6</v>
       </c>
       <c r="E242" s="2">
         <v>44098</v>
@@ -5748,19 +5748,19 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C243" s="1">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="D243" s="1">
-        <v>42.55</v>
+        <v>391.65</v>
       </c>
       <c r="E243" s="2">
-        <v>44112</v>
+        <v>44098</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>120</v>
@@ -5768,19 +5768,19 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C244" s="1">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="D244" s="1">
-        <v>109.95</v>
+        <v>42.55</v>
       </c>
       <c r="E244" s="2">
-        <v>44118</v>
+        <v>44112</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>120</v>
@@ -5794,7 +5794,7 @@
         <v>113</v>
       </c>
       <c r="C245" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D245" s="1">
         <v>109.95</v>
@@ -5808,16 +5808,16 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C246" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D246" s="1">
-        <v>6950</v>
+        <v>109.95</v>
       </c>
       <c r="E246" s="2">
         <v>44118</v>
@@ -5828,7 +5828,7 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>113</v>
@@ -5837,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="D247" s="1">
-        <v>3279.95</v>
+        <v>6950</v>
       </c>
       <c r="E247" s="2">
         <v>44118</v>
@@ -5868,16 +5868,16 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C249" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D249" s="1">
-        <v>2215.0500000000002</v>
+        <v>3279.95</v>
       </c>
       <c r="E249" s="2">
         <v>44118</v>
@@ -5888,16 +5888,16 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C250" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D250" s="1">
-        <v>391.6</v>
+        <v>2215.0500000000002</v>
       </c>
       <c r="E250" s="2">
         <v>44118</v>
@@ -5908,19 +5908,19 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C251" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D251" s="1">
-        <v>2012.4</v>
+        <v>391.6</v>
       </c>
       <c r="E251" s="2">
-        <v>44146</v>
+        <v>44118</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>120</v>
@@ -5928,16 +5928,16 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C252" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D252" s="1">
-        <v>1286.75</v>
+        <v>2012.4</v>
       </c>
       <c r="E252" s="2">
         <v>44146</v>
@@ -5954,10 +5954,10 @@
         <v>117</v>
       </c>
       <c r="C253" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D253" s="1">
-        <v>1286.7</v>
+        <v>1286.75</v>
       </c>
       <c r="E253" s="2">
         <v>44146</v>
@@ -5968,16 +5968,16 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C254" s="1">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D254" s="1">
-        <v>24.9</v>
+        <v>1286.7</v>
       </c>
       <c r="E254" s="2">
         <v>44146</v>
@@ -5988,19 +5988,19 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C255" s="1">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D255" s="1">
-        <v>471.4</v>
+        <v>24.9</v>
       </c>
       <c r="E255" s="2">
-        <v>44147</v>
+        <v>44146</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>120</v>
@@ -6017,7 +6017,7 @@
         <v>25</v>
       </c>
       <c r="D256" s="1">
-        <v>469.3</v>
+        <v>471.4</v>
       </c>
       <c r="E256" s="2">
         <v>44147</v>
@@ -6028,19 +6028,19 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C257" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D257" s="1">
-        <v>1898.9</v>
+        <v>469.3</v>
       </c>
       <c r="E257" s="2">
-        <v>44155</v>
+        <v>44147</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>120</v>
@@ -6048,19 +6048,19 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C258" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D258" s="1">
-        <v>1129.5999999999999</v>
+        <v>1898.9</v>
       </c>
       <c r="E258" s="2">
-        <v>44169</v>
+        <v>44155</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>120</v>
@@ -6068,16 +6068,16 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C259" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D259" s="1">
-        <v>2733.25</v>
+        <v>1129.5999999999999</v>
       </c>
       <c r="E259" s="2">
         <v>44169</v>
@@ -6088,16 +6088,16 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C260" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D260" s="1">
-        <v>1944.2</v>
+        <v>2733.25</v>
       </c>
       <c r="E260" s="2">
         <v>44169</v>
@@ -6108,19 +6108,19 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C261" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D261" s="1">
-        <v>267.05</v>
+        <v>1944.2</v>
       </c>
       <c r="E261" s="2">
-        <v>44174</v>
+        <v>44169</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>120</v>
@@ -6128,19 +6128,19 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C262" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D262" s="1">
-        <v>7739.95</v>
+        <v>267.05</v>
       </c>
       <c r="E262" s="2">
-        <v>44175</v>
+        <v>44174</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>120</v>
@@ -6148,19 +6148,19 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C263" s="1">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="D263" s="1">
-        <v>73.400000000000006</v>
+        <v>7739.95</v>
       </c>
       <c r="E263" s="2">
-        <v>44176</v>
+        <v>44175</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>120</v>
@@ -6168,16 +6168,16 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C264" s="1">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="D264" s="1">
-        <v>2795.65</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="E264" s="2">
         <v>44176</v>
@@ -6188,19 +6188,19 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C265" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D265" s="1">
-        <v>84</v>
+        <v>2795.65</v>
       </c>
       <c r="E265" s="2">
-        <v>44183</v>
+        <v>44176</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>120</v>
@@ -6208,16 +6208,16 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C266" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D266" s="1">
-        <v>630.9</v>
+        <v>84</v>
       </c>
       <c r="E266" s="2">
         <v>44183</v>
@@ -6228,19 +6228,19 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C267" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D267" s="1">
-        <v>506.4</v>
+        <v>630.9</v>
       </c>
       <c r="E267" s="2">
-        <v>44188</v>
+        <v>44183</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>120</v>
@@ -6248,16 +6248,16 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C268" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D268" s="1">
-        <v>155.25</v>
+        <v>506.4</v>
       </c>
       <c r="E268" s="2">
         <v>44188</v>
@@ -6274,7 +6274,7 @@
         <v>113</v>
       </c>
       <c r="C269" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D269" s="1">
         <v>155.25</v>
@@ -6294,7 +6294,7 @@
         <v>113</v>
       </c>
       <c r="C270" s="1">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D270" s="1">
         <v>155.25</v>
@@ -6308,16 +6308,16 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C271" s="1">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D271" s="1">
-        <v>206.1</v>
+        <v>155.25</v>
       </c>
       <c r="E271" s="2">
         <v>44188</v>
@@ -6328,16 +6328,16 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C272" s="1">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="D272" s="1">
-        <v>646.6</v>
+        <v>206.1</v>
       </c>
       <c r="E272" s="2">
         <v>44188</v>
@@ -6348,16 +6348,16 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C273" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D273" s="1">
-        <v>853.9</v>
+        <v>646.6</v>
       </c>
       <c r="E273" s="2">
         <v>44188</v>
@@ -6368,19 +6368,19 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
+        <v>54</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C274" s="1">
         <v>4</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C274" s="1">
-        <v>25</v>
-      </c>
       <c r="D274" s="1">
-        <v>380.5</v>
+        <v>853.9</v>
       </c>
       <c r="E274" s="2">
-        <v>44196</v>
+        <v>44188</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>120</v>
@@ -6388,16 +6388,16 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C275" s="1">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D275" s="1">
-        <v>95.3</v>
+        <v>380.5</v>
       </c>
       <c r="E275" s="2">
         <v>44196</v>
@@ -6408,19 +6408,19 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C276" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D276" s="1">
-        <v>221.7</v>
+        <v>95.3</v>
       </c>
       <c r="E276" s="2">
-        <v>44197</v>
+        <v>44196</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>120</v>
@@ -6428,16 +6428,16 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C277" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="D277" s="1">
-        <v>48.25</v>
+        <v>221.7</v>
       </c>
       <c r="E277" s="2">
         <v>44197</v>
@@ -6454,7 +6454,7 @@
         <v>113</v>
       </c>
       <c r="C278" s="1">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="D278" s="1">
         <v>48.25</v>
@@ -6468,19 +6468,19 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C279" s="1">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D279" s="1">
-        <v>114.05</v>
+        <v>48.25</v>
       </c>
       <c r="E279" s="2">
-        <v>44214</v>
+        <v>44197</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>120</v>
@@ -6488,16 +6488,16 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C280" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D280" s="1">
-        <v>677.35</v>
+        <v>114.05</v>
       </c>
       <c r="E280" s="2">
         <v>44214</v>
@@ -6508,16 +6508,16 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C281" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D281" s="1">
-        <v>38.299999999999997</v>
+        <v>677.35</v>
       </c>
       <c r="E281" s="2">
         <v>44214</v>
@@ -6528,16 +6528,16 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C282" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D282" s="1">
-        <v>256.2</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="E282" s="2">
         <v>44214</v>
@@ -6548,19 +6548,19 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C283" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D283" s="1">
-        <v>261.89999999999998</v>
+        <v>256.2</v>
       </c>
       <c r="E283" s="2">
-        <v>44228</v>
+        <v>44214</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>120</v>
@@ -6568,16 +6568,16 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C284" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D284" s="1">
-        <v>114.7</v>
+        <v>261.89999999999998</v>
       </c>
       <c r="E284" s="2">
         <v>44228</v>
@@ -6588,19 +6588,19 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C285" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D285" s="1">
-        <v>548.20000000000005</v>
+        <v>114.7</v>
       </c>
       <c r="E285" s="2">
-        <v>44238</v>
+        <v>44228</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>120</v>
@@ -6608,16 +6608,16 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C286" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D286" s="1">
-        <v>77.3</v>
+        <v>548.20000000000005</v>
       </c>
       <c r="E286" s="2">
         <v>44238</v>
@@ -6628,16 +6628,16 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
+        <v>61</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C287" s="1">
         <v>50</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C287" s="1">
-        <v>25</v>
-      </c>
       <c r="D287" s="1">
-        <v>87.8</v>
+        <v>77.3</v>
       </c>
       <c r="E287" s="2">
         <v>44238</v>
@@ -6648,19 +6648,19 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C288" s="1">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D288" s="1">
-        <v>1415</v>
+        <v>87.8</v>
       </c>
       <c r="E288" s="2">
-        <v>44258</v>
+        <v>44238</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>120</v>
@@ -6668,16 +6668,16 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C289" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D289" s="1">
-        <v>104.15</v>
+        <v>1415</v>
       </c>
       <c r="E289" s="2">
         <v>44258</v>
@@ -6688,16 +6688,16 @@
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C290" s="1">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="D290" s="1">
-        <v>5.75</v>
+        <v>104.15</v>
       </c>
       <c r="E290" s="2">
         <v>44258</v>
@@ -6708,16 +6708,16 @@
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C291" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D291" s="1">
-        <v>14.2</v>
+        <v>5.75</v>
       </c>
       <c r="E291" s="2">
         <v>44258</v>
@@ -6728,16 +6728,16 @@
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C292" s="1">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D292" s="1">
-        <v>5.75</v>
+        <v>14.2</v>
       </c>
       <c r="E292" s="2">
         <v>44258</v>
@@ -6748,16 +6748,16 @@
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C293" s="1">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="D293" s="1">
-        <v>3168</v>
+        <v>5.75</v>
       </c>
       <c r="E293" s="2">
         <v>44258</v>
@@ -6768,16 +6768,16 @@
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C294" s="1">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D294" s="1">
-        <v>534</v>
+        <v>3168</v>
       </c>
       <c r="E294" s="2">
         <v>44258</v>
@@ -6788,16 +6788,16 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C295" s="1">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D295" s="1">
-        <v>280.39999999999998</v>
+        <v>534</v>
       </c>
       <c r="E295" s="2">
         <v>44258</v>
@@ -6811,13 +6811,13 @@
         <v>39</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C296" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D296" s="1">
-        <v>280.55</v>
+        <v>280.39999999999998</v>
       </c>
       <c r="E296" s="2">
         <v>44258</v>
@@ -6828,16 +6828,16 @@
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C297" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D297" s="1">
-        <v>547.79999999999995</v>
+        <v>280.55</v>
       </c>
       <c r="E297" s="2">
         <v>44258</v>
@@ -6848,19 +6848,19 @@
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C298" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D298" s="1">
-        <v>1336.15</v>
+        <v>547.79999999999995</v>
       </c>
       <c r="E298" s="2">
-        <v>44277</v>
+        <v>44258</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>120</v>
@@ -6868,16 +6868,16 @@
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C299" s="1">
-        <v>800</v>
+        <v>6</v>
       </c>
       <c r="D299" s="1">
-        <v>14.5</v>
+        <v>1336.15</v>
       </c>
       <c r="E299" s="2">
         <v>44277</v>
@@ -6888,16 +6888,16 @@
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C300" s="1">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="D300" s="1">
-        <v>4052.45</v>
+        <v>14.5</v>
       </c>
       <c r="E300" s="2">
         <v>44277</v>
@@ -6908,16 +6908,16 @@
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C301" s="1">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="D301" s="1">
-        <v>5.51</v>
+        <v>4052.45</v>
       </c>
       <c r="E301" s="2">
         <v>44277</v>
@@ -6928,19 +6928,19 @@
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C302" s="1">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="D302" s="1">
-        <v>3135.5</v>
+        <v>5.51</v>
       </c>
       <c r="E302" s="2">
-        <v>44279</v>
+        <v>44277</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>120</v>
@@ -6948,16 +6948,16 @@
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C303" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D303" s="1">
-        <v>981.3</v>
+        <v>3135.5</v>
       </c>
       <c r="E303" s="2">
         <v>44279</v>
@@ -6968,16 +6968,16 @@
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C304" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D304" s="1">
-        <v>113.9</v>
+        <v>981.3</v>
       </c>
       <c r="E304" s="2">
         <v>44279</v>
@@ -6988,16 +6988,16 @@
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C305" s="1">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="D305" s="1">
-        <v>5.6</v>
+        <v>113.9</v>
       </c>
       <c r="E305" s="2">
         <v>44279</v>
@@ -7008,19 +7008,19 @@
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C306" s="1">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="D306" s="1">
-        <v>419.1</v>
+        <v>5.6</v>
       </c>
       <c r="E306" s="2">
-        <v>44280</v>
+        <v>44279</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>120</v>
@@ -7028,19 +7028,19 @@
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C307" s="1">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D307" s="1">
-        <v>114.9</v>
+        <v>419.1</v>
       </c>
       <c r="E307" s="2">
-        <v>44281</v>
+        <v>44280</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>120</v>
@@ -7054,7 +7054,7 @@
         <v>113</v>
       </c>
       <c r="C308" s="1">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D308" s="1">
         <v>114.9</v>
@@ -7074,7 +7074,7 @@
         <v>113</v>
       </c>
       <c r="C309" s="1">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D309" s="1">
         <v>114.9</v>
@@ -7088,16 +7088,16 @@
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C310" s="1">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="D310" s="1">
-        <v>123.05</v>
+        <v>114.9</v>
       </c>
       <c r="E310" s="2">
         <v>44281</v>
@@ -7108,16 +7108,16 @@
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C311" s="1">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="D311" s="1">
-        <v>36.049999999999997</v>
+        <v>123.05</v>
       </c>
       <c r="E311" s="2">
         <v>44281</v>
@@ -7128,16 +7128,16 @@
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C312" s="1">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D312" s="1">
-        <v>14.4</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="E312" s="2">
         <v>44281</v>
@@ -7148,16 +7148,16 @@
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C313" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D313" s="1">
-        <v>396.75</v>
+        <v>14.4</v>
       </c>
       <c r="E313" s="2">
         <v>44281</v>
@@ -7174,10 +7174,10 @@
         <v>117</v>
       </c>
       <c r="C314" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D314" s="1">
-        <v>396.65</v>
+        <v>396.75</v>
       </c>
       <c r="E314" s="2">
         <v>44281</v>
@@ -7188,16 +7188,16 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C315" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D315" s="1">
-        <v>429</v>
+        <v>396.65</v>
       </c>
       <c r="E315" s="2">
         <v>44281</v>
@@ -7208,16 +7208,16 @@
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C316" s="1">
-        <v>575</v>
+        <v>3</v>
       </c>
       <c r="D316" s="1">
-        <v>22.95</v>
+        <v>429</v>
       </c>
       <c r="E316" s="2">
         <v>44281</v>
@@ -7228,16 +7228,16 @@
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C317" s="1">
-        <v>1</v>
+        <v>575</v>
       </c>
       <c r="D317" s="1">
-        <v>6800.2</v>
+        <v>22.95</v>
       </c>
       <c r="E317" s="2">
         <v>44281</v>
@@ -7248,16 +7248,16 @@
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C318" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D318" s="1">
-        <v>199.6</v>
+        <v>6800.2</v>
       </c>
       <c r="E318" s="2">
         <v>44281</v>
@@ -7268,16 +7268,16 @@
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C319" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D319" s="1">
-        <v>36.25</v>
+        <v>199.6</v>
       </c>
       <c r="E319" s="2">
         <v>44281</v>
@@ -7288,16 +7288,16 @@
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C320" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D320" s="1">
-        <v>3598.55</v>
+        <v>36.25</v>
       </c>
       <c r="E320" s="2">
         <v>44281</v>
@@ -7308,16 +7308,16 @@
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C321" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D321" s="1">
-        <v>211</v>
+        <v>3598.55</v>
       </c>
       <c r="E321" s="2">
         <v>44281</v>
@@ -7328,19 +7328,19 @@
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C322" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D322" s="1">
-        <v>890</v>
+        <v>211</v>
       </c>
       <c r="E322" s="2">
-        <v>44286</v>
+        <v>44281</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>120</v>
@@ -7348,19 +7348,19 @@
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C323" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D323" s="1">
-        <v>754.85</v>
+        <v>890</v>
       </c>
       <c r="E323" s="2">
-        <v>44291</v>
+        <v>44286</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>120</v>
@@ -7368,16 +7368,16 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C324" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D324" s="1">
-        <v>2887.05</v>
+        <v>754.85</v>
       </c>
       <c r="E324" s="2">
         <v>44291</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>113</v>
@@ -7397,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="D325" s="1">
-        <v>3506.45</v>
+        <v>2887.05</v>
       </c>
       <c r="E325" s="2">
         <v>44291</v>
@@ -7408,16 +7408,16 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C326" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D326" s="1">
-        <v>677.8</v>
+        <v>3506.45</v>
       </c>
       <c r="E326" s="2">
         <v>44291</v>
@@ -7428,16 +7428,16 @@
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B327" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C327" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D327" s="1">
-        <v>1969.95</v>
+        <v>677.8</v>
       </c>
       <c r="E327" s="2">
         <v>44291</v>
@@ -7448,16 +7448,16 @@
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C328" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D328" s="1">
-        <v>570.1</v>
+        <v>1969.95</v>
       </c>
       <c r="E328" s="2">
         <v>44291</v>
@@ -7468,19 +7468,19 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C329" s="1">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="D329" s="1">
-        <v>207.1</v>
+        <v>570.1</v>
       </c>
       <c r="E329" s="2">
-        <v>44361</v>
+        <v>44291</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>120</v>
@@ -7488,19 +7488,19 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C330" s="1">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="D330" s="1">
-        <v>445</v>
+        <v>207.1</v>
       </c>
       <c r="E330" s="2">
-        <v>44504</v>
+        <v>44361</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>120</v>
@@ -7508,16 +7508,16 @@
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C331" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D331" s="1">
-        <v>151.19999999999999</v>
+        <v>445</v>
       </c>
       <c r="E331" s="2">
         <v>44504</v>
@@ -7528,19 +7528,19 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C332" s="1">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D332" s="1">
-        <v>96.95</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="E332" s="2">
-        <v>44627</v>
+        <v>44504</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>120</v>
@@ -7554,7 +7554,7 @@
         <v>113</v>
       </c>
       <c r="C333" s="1">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D333" s="1">
         <v>96.95</v>
@@ -7568,16 +7568,16 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C334" s="1">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D334" s="1">
-        <v>203.1</v>
+        <v>96.95</v>
       </c>
       <c r="E334" s="2">
         <v>44627</v>
@@ -7588,16 +7588,16 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C335" s="1">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="D335" s="1">
-        <v>306.85000000000002</v>
+        <v>203.1</v>
       </c>
       <c r="E335" s="2">
         <v>44627</v>
@@ -7608,16 +7608,16 @@
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
+        <v>31</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C336" s="1">
         <v>30</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C336" s="1">
-        <v>10</v>
-      </c>
       <c r="D336" s="1">
-        <v>946.85</v>
+        <v>306.85000000000002</v>
       </c>
       <c r="E336" s="2">
         <v>44627</v>
@@ -7628,19 +7628,19 @@
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
+        <v>30</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C337" s="1">
         <v>10</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C337" s="1">
-        <v>4</v>
-      </c>
       <c r="D337" s="1">
-        <v>529.79999999999995</v>
+        <v>946.85</v>
       </c>
       <c r="E337" s="2">
-        <v>44658</v>
+        <v>44627</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>120</v>
@@ -7654,7 +7654,7 @@
         <v>113</v>
       </c>
       <c r="C338" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D338" s="1">
         <v>529.79999999999995</v>
@@ -7674,7 +7674,7 @@
         <v>113</v>
       </c>
       <c r="C339" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D339" s="1">
         <v>529.79999999999995</v>
@@ -7694,7 +7694,7 @@
         <v>113</v>
       </c>
       <c r="C340" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D340" s="1">
         <v>529.79999999999995</v>
@@ -7714,10 +7714,10 @@
         <v>113</v>
       </c>
       <c r="C341" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D341" s="1">
-        <v>529.85</v>
+        <v>529.79999999999995</v>
       </c>
       <c r="E341" s="2">
         <v>44658</v>
@@ -7728,19 +7728,19 @@
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C342" s="1">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="D342" s="1">
-        <v>123.25</v>
+        <v>529.85</v>
       </c>
       <c r="E342" s="2">
-        <v>44697</v>
+        <v>44658</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>120</v>
@@ -7748,16 +7748,16 @@
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C343" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D343" s="1">
-        <v>335.75</v>
+        <v>123.25</v>
       </c>
       <c r="E343" s="2">
         <v>44697</v>
@@ -7768,16 +7768,16 @@
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C344" s="1">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D344" s="1">
-        <v>2586.1</v>
+        <v>335.75</v>
       </c>
       <c r="E344" s="2">
         <v>44697</v>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>117</v>
@@ -7797,7 +7797,7 @@
         <v>3</v>
       </c>
       <c r="D345" s="1">
-        <v>2486.75</v>
+        <v>2586.1</v>
       </c>
       <c r="E345" s="2">
         <v>44697</v>
@@ -7808,16 +7808,16 @@
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C346" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D346" s="1">
-        <v>642.20000000000005</v>
+        <v>2486.75</v>
       </c>
       <c r="E346" s="2">
         <v>44697</v>
@@ -7834,10 +7834,10 @@
         <v>117</v>
       </c>
       <c r="C347" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D347" s="1">
-        <v>642.15</v>
+        <v>642.20000000000005</v>
       </c>
       <c r="E347" s="2">
         <v>44697</v>
@@ -7854,10 +7854,10 @@
         <v>117</v>
       </c>
       <c r="C348" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D348" s="1">
-        <v>642.1</v>
+        <v>642.15</v>
       </c>
       <c r="E348" s="2">
         <v>44697</v>
@@ -7874,10 +7874,10 @@
         <v>117</v>
       </c>
       <c r="C349" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D349" s="1">
-        <v>642.04999999999995</v>
+        <v>642.1</v>
       </c>
       <c r="E349" s="2">
         <v>44697</v>
@@ -7894,10 +7894,10 @@
         <v>117</v>
       </c>
       <c r="C350" s="1">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D350" s="1">
-        <v>642</v>
+        <v>642.04999999999995</v>
       </c>
       <c r="E350" s="2">
         <v>44697</v>
@@ -7908,16 +7908,16 @@
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C351" s="1">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D351" s="1">
-        <v>1483.8</v>
+        <v>642</v>
       </c>
       <c r="E351" s="2">
         <v>44697</v>
@@ -7928,19 +7928,19 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C352" s="1">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D352" s="1">
-        <v>50</v>
+        <v>1483.8</v>
       </c>
       <c r="E352" s="2">
-        <v>44033</v>
+        <v>44697</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>120</v>
@@ -7951,16 +7951,16 @@
         <v>21</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C353" s="1">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D353" s="1">
-        <v>169.75</v>
+        <v>50</v>
       </c>
       <c r="E353" s="2">
-        <v>44697</v>
+        <v>44033</v>
       </c>
       <c r="F353" s="1" t="s">
         <v>120</v>
@@ -7974,10 +7974,10 @@
         <v>117</v>
       </c>
       <c r="C354" s="1">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D354" s="1">
-        <v>169.7</v>
+        <v>169.75</v>
       </c>
       <c r="E354" s="2">
         <v>44697</v>
@@ -7988,19 +7988,19 @@
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C355" s="1">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D355" s="1">
-        <v>0</v>
+        <v>169.7</v>
       </c>
       <c r="E355" s="2">
-        <v>44281</v>
+        <v>44697</v>
       </c>
       <c r="F355" s="1" t="s">
         <v>120</v>
@@ -8008,16 +8008,22 @@
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C356" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D356" s="1">
         <v>0</v>
+      </c>
+      <c r="E356" s="2">
+        <v>44281</v>
+      </c>
+      <c r="F356" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -8025,30 +8031,27 @@
         <v>22</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C357" s="1">
         <v>100</v>
       </c>
       <c r="D357" s="1">
-        <v>61.05</v>
-      </c>
-      <c r="E357" s="2">
-        <v>44697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C358" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D358" s="1">
-        <v>29.5</v>
+        <v>61.05</v>
       </c>
       <c r="E358" s="2">
         <v>44697</v>
@@ -8056,16 +8059,16 @@
     </row>
     <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C359" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D359" s="1">
-        <v>124.2</v>
+        <v>29.5</v>
       </c>
       <c r="E359" s="2">
         <v>44697</v>
@@ -8073,16 +8076,16 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C360" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D360" s="1">
-        <v>2591.35</v>
+        <v>124.2</v>
       </c>
       <c r="E360" s="2">
         <v>44697</v>
@@ -8090,16 +8093,16 @@
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C361" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D361" s="1">
-        <v>503.7</v>
+        <v>2591.35</v>
       </c>
       <c r="E361" s="2">
         <v>44697</v>
@@ -8107,33 +8110,33 @@
     </row>
     <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C362" s="1">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D362" s="1">
-        <v>73.599999999999994</v>
+        <v>503.7</v>
       </c>
       <c r="E362" s="2">
-        <v>44722</v>
+        <v>44697</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C363" s="1">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D363" s="1">
-        <v>181.45</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="E363" s="2">
         <v>44722</v>
@@ -8141,50 +8144,50 @@
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C364" s="1">
-        <v>2000</v>
+        <v>25</v>
       </c>
       <c r="D364" s="1">
-        <v>5.3</v>
+        <v>181.45</v>
       </c>
       <c r="E364" s="2">
-        <v>44802</v>
+        <v>44722</v>
       </c>
     </row>
     <row r="365" spans="1:6">
       <c r="A365" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C365" s="1">
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="D365" s="1">
-        <v>281.75</v>
+        <v>5.3</v>
       </c>
       <c r="E365" s="2">
-        <v>44858</v>
+        <v>44802</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C366" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D366" s="1">
-        <v>7301</v>
+        <v>281.75</v>
       </c>
       <c r="E366" s="2">
         <v>44858</v>
@@ -8192,50 +8195,50 @@
     </row>
     <row r="367" spans="1:6">
       <c r="A367" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C367" s="1">
-        <v>238</v>
+        <v>2</v>
       </c>
       <c r="D367" s="1">
-        <v>6.6</v>
+        <v>7301</v>
       </c>
       <c r="E367" s="2">
-        <v>44894</v>
+        <v>44858</v>
       </c>
     </row>
     <row r="368" spans="1:6">
       <c r="A368" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C368" s="1">
-        <v>3</v>
+        <v>238</v>
       </c>
       <c r="D368" s="1">
-        <v>3629.65</v>
+        <v>6.6</v>
       </c>
       <c r="E368" s="2">
-        <v>45110</v>
+        <v>44894</v>
       </c>
     </row>
     <row r="369" spans="1:5">
       <c r="A369" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C369" s="1">
-        <v>2000</v>
+        <v>3</v>
       </c>
       <c r="D369" s="1">
-        <v>3.05</v>
+        <v>3629.65</v>
       </c>
       <c r="E369" s="2">
         <v>45110</v>
@@ -8243,16 +8246,16 @@
     </row>
     <row r="370" spans="1:5">
       <c r="A370" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C370" s="1">
-        <v>60</v>
+        <v>2000</v>
       </c>
       <c r="D370" s="1">
-        <v>106.3</v>
+        <v>3.05</v>
       </c>
       <c r="E370" s="2">
         <v>45110</v>
@@ -8260,16 +8263,16 @@
     </row>
     <row r="371" spans="1:5">
       <c r="A371" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C371" s="1">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D371" s="1">
-        <v>482.95</v>
+        <v>106.3</v>
       </c>
       <c r="E371" s="2">
         <v>45110</v>
@@ -8277,16 +8280,16 @@
     </row>
     <row r="372" spans="1:5">
       <c r="A372" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C372" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D372" s="1">
-        <v>1182.95</v>
+        <v>482.95</v>
       </c>
       <c r="E372" s="2">
         <v>45110</v>
@@ -8300,7 +8303,7 @@
         <v>117</v>
       </c>
       <c r="C373" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D373" s="1">
         <v>1182.95</v>
@@ -8311,16 +8314,16 @@
     </row>
     <row r="374" spans="1:5">
       <c r="A374" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C374" s="1">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="D374" s="1">
-        <v>85.68</v>
+        <v>1182.95</v>
       </c>
       <c r="E374" s="2">
         <v>45110</v>
@@ -8328,33 +8331,33 @@
     </row>
     <row r="375" spans="1:5">
       <c r="A375" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C375" s="1">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="D375" s="1">
-        <v>152.05000000000001</v>
+        <v>85.68</v>
       </c>
       <c r="E375" s="2">
-        <v>45198</v>
+        <v>45110</v>
       </c>
     </row>
     <row r="376" spans="1:5">
       <c r="A376" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C376" s="1">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="D376" s="1">
-        <v>1161.25</v>
+        <v>152.05000000000001</v>
       </c>
       <c r="E376" s="2">
         <v>45198</v>
@@ -8362,16 +8365,16 @@
     </row>
     <row r="377" spans="1:5">
       <c r="A377" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C377" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D377" s="1">
-        <v>615.6</v>
+        <v>1161.25</v>
       </c>
       <c r="E377" s="2">
         <v>45198</v>
@@ -8385,7 +8388,7 @@
         <v>117</v>
       </c>
       <c r="C378" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D378" s="1">
         <v>615.6</v>
@@ -8396,16 +8399,16 @@
     </row>
     <row r="379" spans="1:5">
       <c r="A379" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C379" s="1">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D379" s="1">
-        <v>633.75</v>
+        <v>615.6</v>
       </c>
       <c r="E379" s="2">
         <v>45198</v>
@@ -8413,16 +8416,16 @@
     </row>
     <row r="380" spans="1:5">
       <c r="A380" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C380" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D380" s="1">
-        <v>1297</v>
+        <v>633.75</v>
       </c>
       <c r="E380" s="2">
         <v>45198</v>
@@ -8430,16 +8433,16 @@
     </row>
     <row r="381" spans="1:5">
       <c r="A381" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C381" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D381" s="1">
-        <v>1938.5</v>
+        <v>1297</v>
       </c>
       <c r="E381" s="2">
         <v>45198</v>
@@ -8447,33 +8450,33 @@
     </row>
     <row r="382" spans="1:5">
       <c r="A382" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C382" s="1">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="D382" s="1">
-        <v>101</v>
+        <v>1938.5</v>
       </c>
       <c r="E382" s="2">
-        <v>45203</v>
+        <v>45198</v>
       </c>
     </row>
     <row r="383" spans="1:5">
       <c r="A383" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C383" s="1">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="D383" s="1">
-        <v>120.85</v>
+        <v>101</v>
       </c>
       <c r="E383" s="2">
         <v>45203</v>
@@ -8487,7 +8490,7 @@
         <v>113</v>
       </c>
       <c r="C384" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D384" s="1">
         <v>120.85</v>
@@ -8504,7 +8507,7 @@
         <v>113</v>
       </c>
       <c r="C385" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D385" s="1">
         <v>120.85</v>
@@ -8521,7 +8524,7 @@
         <v>113</v>
       </c>
       <c r="C386" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D386" s="1">
         <v>120.85</v>
@@ -8538,7 +8541,7 @@
         <v>113</v>
       </c>
       <c r="C387" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D387" s="1">
         <v>120.85</v>
@@ -8555,7 +8558,7 @@
         <v>113</v>
       </c>
       <c r="C388" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D388" s="1">
         <v>120.85</v>
@@ -8623,7 +8626,7 @@
         <v>113</v>
       </c>
       <c r="C392" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D392" s="1">
         <v>120.85</v>
@@ -8640,7 +8643,7 @@
         <v>113</v>
       </c>
       <c r="C393" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D393" s="1">
         <v>120.85</v>
@@ -8691,7 +8694,7 @@
         <v>113</v>
       </c>
       <c r="C396" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D396" s="1">
         <v>120.85</v>
@@ -8708,7 +8711,7 @@
         <v>113</v>
       </c>
       <c r="C397" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D397" s="1">
         <v>120.85</v>
@@ -8776,7 +8779,7 @@
         <v>113</v>
       </c>
       <c r="C401" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D401" s="1">
         <v>120.85</v>
@@ -8793,7 +8796,7 @@
         <v>113</v>
       </c>
       <c r="C402" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D402" s="1">
         <v>120.85</v>
@@ -8810,7 +8813,7 @@
         <v>113</v>
       </c>
       <c r="C403" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D403" s="1">
         <v>120.85</v>
@@ -8827,7 +8830,7 @@
         <v>113</v>
       </c>
       <c r="C404" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D404" s="1">
         <v>120.85</v>
@@ -8861,7 +8864,7 @@
         <v>113</v>
       </c>
       <c r="C406" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D406" s="1">
         <v>120.85</v>
@@ -8878,7 +8881,7 @@
         <v>113</v>
       </c>
       <c r="C407" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D407" s="1">
         <v>120.85</v>
@@ -8929,7 +8932,7 @@
         <v>113</v>
       </c>
       <c r="C410" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D410" s="1">
         <v>120.85</v>
@@ -8946,7 +8949,7 @@
         <v>113</v>
       </c>
       <c r="C411" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D411" s="1">
         <v>120.85</v>
@@ -8957,16 +8960,16 @@
     </row>
     <row r="412" spans="1:5">
       <c r="A412" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C412" s="1">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="D412" s="1">
-        <v>34.5</v>
+        <v>120.85</v>
       </c>
       <c r="E412" s="2">
         <v>45203</v>
@@ -8980,7 +8983,7 @@
         <v>113</v>
       </c>
       <c r="C413" s="1">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="D413" s="1">
         <v>34.5</v>
@@ -8997,7 +9000,7 @@
         <v>113</v>
       </c>
       <c r="C414" s="1">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D414" s="1">
         <v>34.5</v>
@@ -9008,16 +9011,16 @@
     </row>
     <row r="415" spans="1:5">
       <c r="A415" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C415" s="1">
-        <v>900</v>
+        <v>69</v>
       </c>
       <c r="D415" s="1">
-        <v>9.5</v>
+        <v>34.5</v>
       </c>
       <c r="E415" s="2">
         <v>45203</v>
@@ -9031,7 +9034,7 @@
         <v>113</v>
       </c>
       <c r="C416" s="1">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="D416" s="1">
         <v>9.5</v>
@@ -9042,33 +9045,33 @@
     </row>
     <row r="417" spans="1:5">
       <c r="A417" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C417" s="1">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="D417" s="1">
-        <v>74.849999999999994</v>
+        <v>9.5</v>
       </c>
       <c r="E417" s="2">
-        <v>45240</v>
+        <v>45203</v>
       </c>
     </row>
     <row r="418" spans="1:5">
       <c r="A418" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C418" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D418" s="1">
-        <v>173.15</v>
+        <v>74.849999999999994</v>
       </c>
       <c r="E418" s="2">
         <v>45240</v>
@@ -9076,33 +9079,33 @@
     </row>
     <row r="419" spans="1:5">
       <c r="A419" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C419" s="1">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D419" s="1">
-        <v>842.1</v>
+        <v>173.15</v>
       </c>
       <c r="E419" s="2">
-        <v>45242</v>
+        <v>45240</v>
       </c>
     </row>
     <row r="420" spans="1:5">
       <c r="A420" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C420" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D420" s="1">
-        <v>2247.0500000000002</v>
+        <v>842.1</v>
       </c>
       <c r="E420" s="2">
         <v>45242</v>
@@ -9110,16 +9113,16 @@
     </row>
     <row r="421" spans="1:5">
       <c r="A421" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C421" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D421" s="1">
-        <v>2074.35</v>
+        <v>2247.0500000000002</v>
       </c>
       <c r="E421" s="2">
         <v>45242</v>
@@ -9127,16 +9130,16 @@
     </row>
     <row r="422" spans="1:5">
       <c r="A422" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C422" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D422" s="1">
-        <v>123.35</v>
+        <v>2074.35</v>
       </c>
       <c r="E422" s="2">
         <v>45242</v>
@@ -9150,10 +9153,10 @@
         <v>113</v>
       </c>
       <c r="C423" s="1">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D423" s="1">
-        <v>123.4</v>
+        <v>123.35</v>
       </c>
       <c r="E423" s="2">
         <v>45242</v>
@@ -9167,10 +9170,10 @@
         <v>113</v>
       </c>
       <c r="C424" s="1">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D424" s="1">
-        <v>123.45</v>
+        <v>123.4</v>
       </c>
       <c r="E424" s="2">
         <v>45242</v>
@@ -9178,33 +9181,33 @@
     </row>
     <row r="425" spans="1:5">
       <c r="A425" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C425" s="1">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D425" s="1">
-        <v>199.05</v>
+        <v>123.45</v>
       </c>
       <c r="E425" s="2">
-        <v>45246</v>
+        <v>45242</v>
       </c>
     </row>
     <row r="426" spans="1:5">
       <c r="A426" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C426" s="1">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="D426" s="1">
-        <v>619.15</v>
+        <v>199.05</v>
       </c>
       <c r="E426" s="2">
         <v>45246</v>
@@ -9218,10 +9221,10 @@
         <v>117</v>
       </c>
       <c r="C427" s="1">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D427" s="1">
-        <v>619.20000000000005</v>
+        <v>619.15</v>
       </c>
       <c r="E427" s="2">
         <v>45246</v>
@@ -9229,16 +9232,16 @@
     </row>
     <row r="428" spans="1:5">
       <c r="A428" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C428" s="1">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="D428" s="1">
-        <v>356.55</v>
+        <v>619.20000000000005</v>
       </c>
       <c r="E428" s="2">
         <v>45246</v>
@@ -9246,16 +9249,16 @@
     </row>
     <row r="429" spans="1:5">
       <c r="A429" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C429" s="1">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="D429" s="1">
-        <v>953.9</v>
+        <v>356.55</v>
       </c>
       <c r="E429" s="2">
         <v>45246</v>
@@ -9269,10 +9272,10 @@
         <v>117</v>
       </c>
       <c r="C430" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D430" s="1">
-        <v>953.95</v>
+        <v>953.9</v>
       </c>
       <c r="E430" s="2">
         <v>45246</v>
@@ -9286,10 +9289,10 @@
         <v>117</v>
       </c>
       <c r="C431" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D431" s="1">
-        <v>953.9</v>
+        <v>953.95</v>
       </c>
       <c r="E431" s="2">
         <v>45246</v>
@@ -9306,7 +9309,7 @@
         <v>3</v>
       </c>
       <c r="D432" s="1">
-        <v>953.6</v>
+        <v>953.9</v>
       </c>
       <c r="E432" s="2">
         <v>45246</v>
@@ -9314,16 +9317,16 @@
     </row>
     <row r="433" spans="1:5">
       <c r="A433" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C433" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D433" s="1">
-        <v>311.10000000000002</v>
+        <v>953.6</v>
       </c>
       <c r="E433" s="2">
         <v>45246</v>
@@ -9337,7 +9340,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="1">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="D434" s="1">
         <v>311.10000000000002</v>
@@ -9348,33 +9351,33 @@
     </row>
     <row r="435" spans="1:5">
       <c r="A435" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C435" s="1">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D435" s="1">
-        <v>5437.25</v>
+        <v>311.10000000000002</v>
       </c>
       <c r="E435" s="2">
-        <v>45247</v>
+        <v>45246</v>
       </c>
     </row>
     <row r="436" spans="1:5">
       <c r="A436" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C436" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D436" s="1">
-        <v>142.9</v>
+        <v>5437.25</v>
       </c>
       <c r="E436" s="2">
         <v>45247</v>
@@ -9382,33 +9385,33 @@
     </row>
     <row r="437" spans="1:5">
       <c r="A437" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C437" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D437" s="1">
-        <v>144.15</v>
+        <v>142.9</v>
       </c>
       <c r="E437" s="2">
-        <v>45329</v>
+        <v>45247</v>
       </c>
     </row>
     <row r="438" spans="1:5">
       <c r="A438" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C438" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D438" s="1">
-        <v>142.9</v>
+        <v>144.15</v>
       </c>
       <c r="E438" s="2">
         <v>45329</v>
@@ -9416,16 +9419,16 @@
     </row>
     <row r="439" spans="1:5">
       <c r="A439" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C439" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D439" s="1">
-        <v>279.05</v>
+        <v>142.9</v>
       </c>
       <c r="E439" s="2">
         <v>45329</v>
@@ -9433,16 +9436,16 @@
     </row>
     <row r="440" spans="1:5">
       <c r="A440" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C440" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D440" s="1">
-        <v>862.05</v>
+        <v>279.05</v>
       </c>
       <c r="E440" s="2">
         <v>45329</v>
@@ -9456,7 +9459,7 @@
         <v>117</v>
       </c>
       <c r="C441" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D441" s="1">
         <v>862.05</v>
@@ -9473,10 +9476,10 @@
         <v>117</v>
       </c>
       <c r="C442" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D442" s="1">
-        <v>862.1</v>
+        <v>862.05</v>
       </c>
       <c r="E442" s="2">
         <v>45329</v>
@@ -9484,16 +9487,16 @@
     </row>
     <row r="443" spans="1:5">
       <c r="A443" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C443" s="1">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D443" s="1">
-        <v>1017.95</v>
+        <v>862.1</v>
       </c>
       <c r="E443" s="2">
         <v>45329</v>
@@ -9501,16 +9504,16 @@
     </row>
     <row r="444" spans="1:5">
       <c r="A444" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C444" s="1">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D444" s="1">
-        <v>2867.5</v>
+        <v>1017.95</v>
       </c>
       <c r="E444" s="2">
         <v>45329</v>
@@ -9524,10 +9527,10 @@
         <v>117</v>
       </c>
       <c r="C445" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D445" s="1">
-        <v>2867.2</v>
+        <v>2867.5</v>
       </c>
       <c r="E445" s="2">
         <v>45329</v>
@@ -9535,16 +9538,16 @@
     </row>
     <row r="446" spans="1:5">
       <c r="A446" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C446" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D446" s="1">
-        <v>10796.1</v>
+        <v>2867.2</v>
       </c>
       <c r="E446" s="2">
         <v>45329</v>
@@ -9552,16 +9555,16 @@
     </row>
     <row r="447" spans="1:5">
       <c r="A447" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C447" s="1">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D447" s="1">
-        <v>88.1</v>
+        <v>10796.1</v>
       </c>
       <c r="E447" s="2">
         <v>45329</v>
@@ -9575,7 +9578,7 @@
         <v>113</v>
       </c>
       <c r="C448" s="1">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="D448" s="1">
         <v>88.1</v>
@@ -9586,16 +9589,16 @@
     </row>
     <row r="449" spans="1:5">
       <c r="A449" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B449" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C449" s="1">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="D449" s="1">
-        <v>69.099999999999994</v>
+        <v>88.1</v>
       </c>
       <c r="E449" s="2">
         <v>45329</v>
@@ -9609,7 +9612,7 @@
         <v>113</v>
       </c>
       <c r="C450" s="1">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D450" s="1">
         <v>69.099999999999994</v>
@@ -9626,7 +9629,7 @@
         <v>113</v>
       </c>
       <c r="C451" s="1">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="D451" s="1">
         <v>69.099999999999994</v>
@@ -9637,16 +9640,16 @@
     </row>
     <row r="452" spans="1:5">
       <c r="A452" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C452" s="1">
-        <v>500</v>
+        <v>195</v>
       </c>
       <c r="D452" s="1">
-        <v>52.5</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="E452" s="2">
         <v>45329</v>
@@ -9654,16 +9657,16 @@
     </row>
     <row r="453" spans="1:5">
       <c r="A453" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C453" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D453" s="1">
-        <v>58.15</v>
+        <v>52.5</v>
       </c>
       <c r="E453" s="2">
         <v>45329</v>
@@ -9671,16 +9674,16 @@
     </row>
     <row r="454" spans="1:5">
       <c r="A454" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C454" s="1">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="D454" s="1">
-        <v>97.25</v>
+        <v>58.15</v>
       </c>
       <c r="E454" s="2">
         <v>45329</v>
@@ -9688,16 +9691,16 @@
     </row>
     <row r="455" spans="1:5">
       <c r="A455" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C455" s="1">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D455" s="1">
-        <v>140.05000000000001</v>
+        <v>97.25</v>
       </c>
       <c r="E455" s="2">
         <v>45329</v>
@@ -9705,33 +9708,33 @@
     </row>
     <row r="456" spans="1:5">
       <c r="A456" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C456" s="1">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D456" s="1">
-        <v>1897</v>
+        <v>140.05000000000001</v>
       </c>
       <c r="E456" s="2">
-        <v>45330</v>
+        <v>45329</v>
       </c>
     </row>
     <row r="457" spans="1:5">
       <c r="A457" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C457" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D457" s="1">
-        <v>7734.65</v>
+        <v>1897</v>
       </c>
       <c r="E457" s="2">
         <v>45330</v>
@@ -9739,16 +9742,16 @@
     </row>
     <row r="458" spans="1:5">
       <c r="A458" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C458" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D458" s="1">
-        <v>2009.7</v>
+        <v>7734.65</v>
       </c>
       <c r="E458" s="2">
         <v>45330</v>
@@ -9756,33 +9759,33 @@
     </row>
     <row r="459" spans="1:5">
       <c r="A459" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C459" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D459" s="1">
-        <v>2860</v>
+        <v>2009.7</v>
       </c>
       <c r="E459" s="2">
-        <v>45334</v>
+        <v>45330</v>
       </c>
     </row>
     <row r="460" spans="1:5">
       <c r="A460" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C460" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D460" s="1">
-        <v>483.95</v>
+        <v>2860</v>
       </c>
       <c r="E460" s="2">
         <v>45334</v>
@@ -9790,33 +9793,33 @@
     </row>
     <row r="461" spans="1:5">
       <c r="A461" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C461" s="1">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D461" s="1">
-        <v>271</v>
+        <v>483.95</v>
       </c>
       <c r="E461" s="2">
-        <v>45408</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="462" spans="1:5">
       <c r="A462" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C462" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D462" s="1">
-        <v>30.25</v>
+        <v>271</v>
       </c>
       <c r="E462" s="2">
         <v>45408</v>
@@ -9830,7 +9833,7 @@
         <v>113</v>
       </c>
       <c r="C463" s="1">
-        <v>390</v>
+        <v>40</v>
       </c>
       <c r="D463" s="1">
         <v>30.25</v>
@@ -9841,16 +9844,16 @@
     </row>
     <row r="464" spans="1:5">
       <c r="A464" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C464" s="1">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="D464" s="1">
-        <v>168</v>
+        <v>30.25</v>
       </c>
       <c r="E464" s="2">
         <v>45408</v>
@@ -9858,16 +9861,16 @@
     </row>
     <row r="465" spans="1:5">
       <c r="A465" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C465" s="1">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D465" s="1">
-        <v>30.45</v>
+        <v>168</v>
       </c>
       <c r="E465" s="2">
         <v>45408</v>
@@ -9875,16 +9878,16 @@
     </row>
     <row r="466" spans="1:5">
       <c r="A466" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C466" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D466" s="1">
-        <v>933.75</v>
+        <v>30.45</v>
       </c>
       <c r="E466" s="2">
         <v>45408</v>
@@ -9892,24 +9895,24 @@
     </row>
     <row r="467" spans="1:5">
       <c r="A467" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C467" s="1">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D467" s="1">
-        <v>300.3</v>
+        <v>933.75</v>
       </c>
       <c r="E467" s="2">
-        <v>45415</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="468" spans="1:5">
       <c r="A468" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>113</v>
@@ -9918,7 +9921,7 @@
         <v>70</v>
       </c>
       <c r="D468" s="1">
-        <v>19.75</v>
+        <v>300.3</v>
       </c>
       <c r="E468" s="2">
         <v>45415</v>
@@ -9926,36 +9929,36 @@
     </row>
     <row r="469" spans="1:5">
       <c r="A469" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C469" s="1">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D469" s="1">
-        <v>269.10000000000002</v>
+        <v>19.75</v>
       </c>
       <c r="E469" s="2">
-        <v>45425</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="470" spans="1:5">
       <c r="A470" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C470" s="1">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="D470" s="1">
-        <v>42.64</v>
+        <v>269.10000000000002</v>
       </c>
       <c r="E470" s="2">
-        <v>45462</v>
+        <v>45425</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -9966,7 +9969,7 @@
         <v>113</v>
       </c>
       <c r="C471" s="1">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="D471" s="1">
         <v>42.64</v>
@@ -9983,7 +9986,7 @@
         <v>113</v>
       </c>
       <c r="C472" s="1">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="D472" s="1">
         <v>42.64</v>
@@ -9994,16 +9997,16 @@
     </row>
     <row r="473" spans="1:5">
       <c r="A473" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C473" s="1">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="D473" s="1">
-        <v>126.84</v>
+        <v>42.64</v>
       </c>
       <c r="E473" s="2">
         <v>45462</v>
@@ -10011,16 +10014,16 @@
     </row>
     <row r="474" spans="1:5">
       <c r="A474" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C474" s="1">
-        <v>312</v>
+        <v>170</v>
       </c>
       <c r="D474" s="1">
-        <v>51.37</v>
+        <v>126.84</v>
       </c>
       <c r="E474" s="2">
         <v>45462</v>
@@ -10034,7 +10037,7 @@
         <v>113</v>
       </c>
       <c r="C475" s="1">
-        <v>88</v>
+        <v>312</v>
       </c>
       <c r="D475" s="1">
         <v>51.37</v>
@@ -10045,67 +10048,67 @@
     </row>
     <row r="476" spans="1:5">
       <c r="A476" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C476" s="1">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D476" s="1">
-        <v>825.9</v>
-      </c>
-      <c r="E476" s="2" t="s">
-        <v>128</v>
+        <v>51.37</v>
+      </c>
+      <c r="E476" s="2">
+        <v>45462</v>
       </c>
     </row>
     <row r="477" spans="1:5">
       <c r="A477" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C477" s="1">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="D477" s="1">
-        <v>10.53</v>
+        <v>825.9</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="478" spans="1:5">
       <c r="A478" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C478" s="1">
-        <v>40</v>
+        <v>480</v>
       </c>
       <c r="D478" s="1">
-        <v>351.85</v>
+        <v>10.53</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="479" spans="1:5">
       <c r="A479" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C479" s="1">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D479" s="1">
-        <v>402.95</v>
+        <v>351.85</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>131</v>
@@ -10113,24 +10116,24 @@
     </row>
     <row r="480" spans="1:5">
       <c r="A480" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C480" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D480" s="1">
-        <v>431.2</v>
+        <v>402.95</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="481" spans="1:5">
       <c r="A481" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>113</v>
@@ -10139,7 +10142,7 @@
         <v>1</v>
       </c>
       <c r="D481" s="1">
-        <v>797.05</v>
+        <v>431.2</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>133</v>
@@ -10147,7 +10150,7 @@
     </row>
     <row r="482" spans="1:5">
       <c r="A482" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>113</v>
@@ -10156,7 +10159,7 @@
         <v>1</v>
       </c>
       <c r="D482" s="1">
-        <v>168.7</v>
+        <v>797.05</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>133</v>
@@ -10164,7 +10167,7 @@
     </row>
     <row r="483" spans="1:5">
       <c r="A483" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>113</v>
@@ -10173,7 +10176,7 @@
         <v>1</v>
       </c>
       <c r="D483" s="1">
-        <v>276.64999999999998</v>
+        <v>168.7</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>133</v>
@@ -10181,7 +10184,7 @@
     </row>
     <row r="484" spans="1:5">
       <c r="A484" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>113</v>
@@ -10190,7 +10193,7 @@
         <v>1</v>
       </c>
       <c r="D484" s="1">
-        <v>93.17</v>
+        <v>276.64999999999998</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>133</v>
@@ -10198,7 +10201,7 @@
     </row>
     <row r="485" spans="1:5">
       <c r="A485" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>113</v>
@@ -10207,7 +10210,7 @@
         <v>1</v>
       </c>
       <c r="D485" s="1">
-        <v>126.56</v>
+        <v>93.17</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>133</v>
@@ -10215,7 +10218,7 @@
     </row>
     <row r="486" spans="1:5">
       <c r="A486" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>113</v>
@@ -10224,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="D486" s="1">
-        <v>295.39999999999998</v>
+        <v>126.56</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>133</v>
@@ -10232,7 +10235,7 @@
     </row>
     <row r="487" spans="1:5">
       <c r="A487" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>113</v>
@@ -10241,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="D487" s="1">
-        <v>107.58</v>
+        <v>295.39999999999998</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>133</v>
@@ -10249,7 +10252,7 @@
     </row>
     <row r="488" spans="1:5">
       <c r="A488" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>113</v>
@@ -10258,7 +10261,7 @@
         <v>1</v>
       </c>
       <c r="D488" s="1">
-        <v>496.8</v>
+        <v>107.58</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>133</v>
@@ -10266,7 +10269,7 @@
     </row>
     <row r="489" spans="1:5">
       <c r="A489" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>113</v>
@@ -10275,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="D489" s="1">
-        <v>5501.15</v>
+        <v>496.8</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>133</v>
@@ -10283,7 +10286,7 @@
     </row>
     <row r="490" spans="1:5">
       <c r="A490" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>113</v>
@@ -10292,7 +10295,7 @@
         <v>1</v>
       </c>
       <c r="D490" s="1">
-        <v>1658.4</v>
+        <v>5501.15</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>133</v>
@@ -10300,7 +10303,7 @@
     </row>
     <row r="491" spans="1:5">
       <c r="A491" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>113</v>
@@ -10309,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="D491" s="1">
-        <v>1933.2</v>
+        <v>1658.4</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>133</v>
@@ -10317,7 +10320,7 @@
     </row>
     <row r="492" spans="1:5">
       <c r="A492" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>113</v>
@@ -10326,10 +10329,10 @@
         <v>1</v>
       </c>
       <c r="D492" s="1">
-        <v>1651.65</v>
+        <v>1933.2</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -10428,7 +10431,7 @@
         <v>1</v>
       </c>
       <c r="D498" s="1">
-        <v>1651.7</v>
+        <v>1651.65</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>140</v>
@@ -10445,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="D499" s="1">
-        <v>1651.65</v>
+        <v>1651.7</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>140</v>
@@ -10453,7 +10456,7 @@
     </row>
     <row r="500" spans="1:5">
       <c r="A500" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B500" s="1" t="s">
         <v>113</v>
@@ -10462,7 +10465,7 @@
         <v>1</v>
       </c>
       <c r="D500" s="1">
-        <v>4149.1000000000004</v>
+        <v>1651.65</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>140</v>
@@ -10479,7 +10482,7 @@
         <v>1</v>
       </c>
       <c r="D501" s="1">
-        <v>4149.05</v>
+        <v>4149.1000000000004</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>140</v>
@@ -10496,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="D502" s="1">
-        <v>4149.1000000000004</v>
+        <v>4149.05</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>140</v>
@@ -10504,16 +10507,16 @@
     </row>
     <row r="503" spans="1:5">
       <c r="A503" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="B503" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C503" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D503" s="1">
-        <v>333.65</v>
+        <v>4149.1000000000004</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>140</v>
@@ -10521,16 +10524,16 @@
     </row>
     <row r="504" spans="1:5">
       <c r="A504" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C504" s="1">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D504" s="1">
-        <v>4851.55</v>
+        <v>333.65</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>140</v>
@@ -10544,7 +10547,7 @@
         <v>113</v>
       </c>
       <c r="C505" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D505" s="1">
         <v>4851.55</v>
@@ -10555,16 +10558,16 @@
     </row>
     <row r="506" spans="1:5">
       <c r="A506" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C506" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D506" s="1">
-        <v>1563.25</v>
+        <v>4851.55</v>
       </c>
       <c r="E506" s="2" t="s">
         <v>140</v>
@@ -10572,16 +10575,16 @@
     </row>
     <row r="507" spans="1:5">
       <c r="A507" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C507" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D507" s="1">
-        <v>90.01</v>
+        <v>1563.25</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>140</v>
@@ -10589,16 +10592,16 @@
     </row>
     <row r="508" spans="1:5">
       <c r="A508" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C508" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D508" s="1">
-        <v>1024.3499999999999</v>
+        <v>90.01</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>140</v>
@@ -10606,16 +10609,16 @@
     </row>
     <row r="509" spans="1:5">
       <c r="A509" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C509" s="1">
-        <v>600</v>
+        <v>20</v>
       </c>
       <c r="D509" s="1">
-        <v>18.78</v>
+        <v>1024.3499999999999</v>
       </c>
       <c r="E509" s="2" t="s">
         <v>140</v>
@@ -10623,16 +10626,16 @@
     </row>
     <row r="510" spans="1:5">
       <c r="A510" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B510" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C510" s="1">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="D510" s="1">
-        <v>170.43</v>
+        <v>18.78</v>
       </c>
       <c r="E510" s="2" t="s">
         <v>140</v>
@@ -10640,16 +10643,16 @@
     </row>
     <row r="511" spans="1:5">
       <c r="A511" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B511" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C511" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D511" s="1">
-        <v>263.3</v>
+        <v>170.43</v>
       </c>
       <c r="E511" s="2" t="s">
         <v>140</v>
@@ -10657,16 +10660,16 @@
     </row>
     <row r="512" spans="1:5">
       <c r="A512" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C512" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D512" s="1">
-        <v>865.55</v>
+        <v>263.3</v>
       </c>
       <c r="E512" s="2" t="s">
         <v>140</v>
@@ -10680,10 +10683,10 @@
         <v>113</v>
       </c>
       <c r="C513" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D513" s="1">
-        <v>865.6</v>
+        <v>865.55</v>
       </c>
       <c r="E513" s="2" t="s">
         <v>140</v>
@@ -10691,16 +10694,16 @@
     </row>
     <row r="514" spans="1:5">
       <c r="A514" t="s">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="B514" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C514" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D514" s="1">
-        <v>9.15</v>
+        <v>865.6</v>
       </c>
       <c r="E514" s="2" t="s">
         <v>140</v>
@@ -10708,19 +10711,19 @@
     </row>
     <row r="515" spans="1:5">
       <c r="A515" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="B515" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C515" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D515" s="1">
-        <v>18.3</v>
+        <v>9.15</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -10731,10 +10734,10 @@
         <v>113</v>
       </c>
       <c r="C516" s="1">
-        <v>499</v>
+        <v>1</v>
       </c>
       <c r="D516" s="1">
-        <v>18.309999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="E516" s="2" t="s">
         <v>147</v>
@@ -10742,16 +10745,16 @@
     </row>
     <row r="517" spans="1:5">
       <c r="A517" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="B517" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C517" s="1">
-        <v>4</v>
+        <v>499</v>
       </c>
       <c r="D517" s="1">
-        <v>1454.1</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="E517" s="2" t="s">
         <v>147</v>
@@ -10759,16 +10762,16 @@
     </row>
     <row r="518" spans="1:5">
       <c r="A518" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C518" s="1">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D518" s="1">
-        <v>81.2</v>
+        <v>1454.1</v>
       </c>
       <c r="E518" s="2" t="s">
         <v>147</v>
@@ -10776,16 +10779,16 @@
     </row>
     <row r="519" spans="1:5">
       <c r="A519" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B519" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C519" s="1">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D519" s="1">
-        <v>78.64</v>
+        <v>81.2</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>147</v>
@@ -10799,7 +10802,7 @@
         <v>113</v>
       </c>
       <c r="C520" s="1">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D520" s="1">
         <v>78.64</v>
@@ -10816,7 +10819,7 @@
         <v>113</v>
       </c>
       <c r="C521" s="1">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D521" s="1">
         <v>78.64</v>
@@ -10833,7 +10836,7 @@
         <v>113</v>
       </c>
       <c r="C522" s="1">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="D522" s="1">
         <v>78.64</v>
@@ -10850,7 +10853,7 @@
         <v>113</v>
       </c>
       <c r="C523" s="1">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D523" s="1">
         <v>78.64</v>
@@ -10861,16 +10864,16 @@
     </row>
     <row r="524" spans="1:5">
       <c r="A524" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C524" s="1">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D524" s="1">
-        <v>23.77</v>
+        <v>78.64</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>147</v>
@@ -10884,7 +10887,7 @@
         <v>113</v>
       </c>
       <c r="C525" s="1">
-        <v>195</v>
+        <v>5</v>
       </c>
       <c r="D525" s="1">
         <v>23.77</v>
@@ -10895,16 +10898,16 @@
     </row>
     <row r="526" spans="1:5">
       <c r="A526" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C526" s="1">
-        <v>300</v>
+        <v>195</v>
       </c>
       <c r="D526" s="1">
-        <v>51.25</v>
+        <v>23.77</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>147</v>
@@ -10912,16 +10915,16 @@
     </row>
     <row r="527" spans="1:5">
       <c r="A527" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C527" s="1">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="D527" s="1">
-        <v>462.85</v>
+        <v>51.25</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>147</v>
@@ -10929,33 +10932,33 @@
     </row>
     <row r="528" spans="1:5">
       <c r="A528" t="s">
-        <v>149</v>
+        <v>12</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C528" s="1">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="D528" s="1">
-        <v>88.28</v>
+        <v>462.85</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="529" spans="1:5">
       <c r="A529" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C529" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D529" s="1">
-        <v>42</v>
+        <v>88.28</v>
       </c>
       <c r="E529" s="2" t="s">
         <v>150</v>
@@ -10963,16 +10966,16 @@
     </row>
     <row r="530" spans="1:5">
       <c r="A530" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C530" s="1">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="D530" s="1">
-        <v>1496.65</v>
+        <v>42</v>
       </c>
       <c r="E530" s="2" t="s">
         <v>150</v>
@@ -10980,16 +10983,16 @@
     </row>
     <row r="531" spans="1:5">
       <c r="A531" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C531" s="1">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D531" s="1">
-        <v>22.53</v>
+        <v>1496.65</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>150</v>
@@ -10997,16 +11000,16 @@
     </row>
     <row r="532" spans="1:5">
       <c r="A532" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C532" s="1">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D532" s="1">
-        <v>250.6</v>
+        <v>22.53</v>
       </c>
       <c r="E532" s="2" t="s">
         <v>150</v>
@@ -11014,16 +11017,16 @@
     </row>
     <row r="533" spans="1:5">
       <c r="A533" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C533" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D533" s="1">
-        <v>31.83</v>
+        <v>250.6</v>
       </c>
       <c r="E533" s="2" t="s">
         <v>150</v>
@@ -11031,16 +11034,16 @@
     </row>
     <row r="534" spans="1:5">
       <c r="A534" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C534" s="1">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D534" s="1">
-        <v>271.64999999999998</v>
+        <v>31.83</v>
       </c>
       <c r="E534" s="2" t="s">
         <v>150</v>
@@ -11048,33 +11051,33 @@
     </row>
     <row r="535" spans="1:5">
       <c r="A535" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C535" s="1">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D535" s="1">
-        <v>6201.3</v>
+        <v>271.64999999999998</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="536" spans="1:5">
       <c r="A536" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C536" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D536" s="1">
-        <v>719.35</v>
+        <v>6201.3</v>
       </c>
       <c r="E536" s="2" t="s">
         <v>154</v>
@@ -11082,16 +11085,16 @@
     </row>
     <row r="537" spans="1:5">
       <c r="A537" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B537" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C537" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D537" s="1">
-        <v>1658.15</v>
+        <v>719.35</v>
       </c>
       <c r="E537" s="2" t="s">
         <v>154</v>
@@ -11099,16 +11102,16 @@
     </row>
     <row r="538" spans="1:5">
       <c r="A538" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B538" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C538" s="1">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D538" s="1">
-        <v>19.39</v>
+        <v>1658.15</v>
       </c>
       <c r="E538" s="2" t="s">
         <v>154</v>
@@ -11122,7 +11125,7 @@
         <v>113</v>
       </c>
       <c r="C539" s="1">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D539" s="1">
         <v>19.39</v>
@@ -11173,7 +11176,7 @@
         <v>113</v>
       </c>
       <c r="C542" s="1">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D542" s="1">
         <v>19.39</v>
@@ -11190,7 +11193,7 @@
         <v>113</v>
       </c>
       <c r="C543" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D543" s="1">
         <v>19.39</v>
@@ -11201,16 +11204,16 @@
     </row>
     <row r="544" spans="1:5">
       <c r="A544" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C544" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D544" s="1">
-        <v>751.3</v>
+        <v>19.39</v>
       </c>
       <c r="E544" s="2" t="s">
         <v>154</v>
@@ -11218,7 +11221,7 @@
     </row>
     <row r="545" spans="1:5">
       <c r="A545" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B545" s="1" t="s">
         <v>113</v>
@@ -11227,7 +11230,7 @@
         <v>5</v>
       </c>
       <c r="D545" s="1">
-        <v>814.15</v>
+        <v>751.3</v>
       </c>
       <c r="E545" s="2" t="s">
         <v>154</v>
@@ -11235,70 +11238,70 @@
     </row>
     <row r="546" spans="1:5">
       <c r="A546" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C546" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D546" s="1">
-        <v>6492.65</v>
+        <v>814.15</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="547" spans="1:5">
       <c r="A547" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C547" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D547" s="1">
-        <v>798.35</v>
+        <v>6492.65</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="548" spans="1:5">
       <c r="A548" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B548" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C548" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D548" s="1">
-        <v>32.58</v>
+        <v>798.35</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="549" spans="1:5">
       <c r="A549" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C549" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D549" s="1">
-        <v>56.18</v>
+        <v>32.58</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="550" spans="1:5">
@@ -11309,10 +11312,10 @@
         <v>117</v>
       </c>
       <c r="C550" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D550" s="1">
-        <v>56.16</v>
+        <v>56.18</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>165</v>
@@ -11326,10 +11329,10 @@
         <v>117</v>
       </c>
       <c r="C551" s="1">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D551" s="1">
-        <v>56.22</v>
+        <v>56.16</v>
       </c>
       <c r="E551" s="2" t="s">
         <v>165</v>
@@ -11343,10 +11346,10 @@
         <v>117</v>
       </c>
       <c r="C552" s="1">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D552" s="1">
-        <v>56.15</v>
+        <v>56.22</v>
       </c>
       <c r="E552" s="2" t="s">
         <v>165</v>
@@ -11360,10 +11363,10 @@
         <v>117</v>
       </c>
       <c r="C553" s="1">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="D553" s="1">
-        <v>56.2</v>
+        <v>56.15</v>
       </c>
       <c r="E553" s="2" t="s">
         <v>165</v>
@@ -11377,10 +11380,10 @@
         <v>117</v>
       </c>
       <c r="C554" s="1">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="D554" s="1">
-        <v>56.19</v>
+        <v>56.2</v>
       </c>
       <c r="E554" s="2" t="s">
         <v>165</v>
@@ -11388,19 +11391,19 @@
     </row>
     <row r="555" spans="1:5">
       <c r="A555" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C555" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D555" s="1">
-        <v>65.180000000000007</v>
+        <v>56.19</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="556" spans="1:5">
@@ -11411,10 +11414,10 @@
         <v>113</v>
       </c>
       <c r="C556" s="1">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="D556" s="1">
-        <v>65.19</v>
+        <v>65.180000000000007</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>166</v>
@@ -11422,50 +11425,50 @@
     </row>
     <row r="557" spans="1:5">
       <c r="A557" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C557" s="1">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="D557" s="1">
-        <v>722.7</v>
+        <v>65.19</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="558" spans="1:5">
       <c r="A558" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C558" s="1">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="D558" s="1">
-        <v>41.47</v>
+        <v>722.7</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="559" spans="1:5">
       <c r="A559" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B559" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C559" s="1">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="D559" s="1">
-        <v>1223.45</v>
+        <v>41.47</v>
       </c>
       <c r="E559" s="2" t="s">
         <v>168</v>
@@ -11473,16 +11476,16 @@
     </row>
     <row r="560" spans="1:5">
       <c r="A560" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B560" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C560" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D560" s="1">
-        <v>1203.05</v>
+        <v>1223.45</v>
       </c>
       <c r="E560" s="2" t="s">
         <v>168</v>
@@ -11490,16 +11493,16 @@
     </row>
     <row r="561" spans="1:5">
       <c r="A561" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C561" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D561" s="1">
-        <v>570.20000000000005</v>
+        <v>1203.05</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>168</v>
@@ -11507,16 +11510,16 @@
     </row>
     <row r="562" spans="1:5">
       <c r="A562" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C562" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D562" s="1">
-        <v>3661.1</v>
+        <v>570.20000000000005</v>
       </c>
       <c r="E562" s="2" t="s">
         <v>168</v>
@@ -11524,16 +11527,16 @@
     </row>
     <row r="563" spans="1:5">
       <c r="A563" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="B563" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C563" s="1">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D563" s="1">
-        <v>651.4</v>
+        <v>3661.1</v>
       </c>
       <c r="E563" s="2" t="s">
         <v>168</v>
@@ -11541,16 +11544,16 @@
     </row>
     <row r="564" spans="1:5">
       <c r="A564" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C564" s="1">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D564" s="1">
-        <v>309.95</v>
+        <v>651.4</v>
       </c>
       <c r="E564" s="2" t="s">
         <v>168</v>
@@ -11564,10 +11567,10 @@
         <v>113</v>
       </c>
       <c r="C565" s="1">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D565" s="1">
-        <v>309.85000000000002</v>
+        <v>309.95</v>
       </c>
       <c r="E565" s="2" t="s">
         <v>168</v>
@@ -11581,10 +11584,10 @@
         <v>113</v>
       </c>
       <c r="C566" s="1">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D566" s="1">
-        <v>309.95</v>
+        <v>309.85000000000002</v>
       </c>
       <c r="E566" s="2" t="s">
         <v>168</v>
@@ -11592,16 +11595,16 @@
     </row>
     <row r="567" spans="1:5">
       <c r="A567" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B567" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C567" s="1">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D567" s="1">
-        <v>71.739999999999995</v>
+        <v>309.95</v>
       </c>
       <c r="E567" s="2" t="s">
         <v>168</v>
@@ -11609,16 +11612,16 @@
     </row>
     <row r="568" spans="1:5">
       <c r="A568" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B568" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C568" s="1">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D568" s="1">
-        <v>1033.6500000000001</v>
+        <v>71.739999999999995</v>
       </c>
       <c r="E568" s="2" t="s">
         <v>168</v>
@@ -11626,24 +11629,24 @@
     </row>
     <row r="569" spans="1:5">
       <c r="A569" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C569" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D569" s="1">
-        <v>92.83</v>
-      </c>
-      <c r="E569" s="2">
-        <v>45873</v>
+        <v>1033.6500000000001</v>
+      </c>
+      <c r="E569" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="570" spans="1:5">
       <c r="A570" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B570" s="1" t="s">
         <v>117</v>
@@ -11652,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="D570" s="1">
-        <v>141.94999999999999</v>
+        <v>92.83</v>
       </c>
       <c r="E570" s="2">
         <v>45873</v>
@@ -11660,7 +11663,7 @@
     </row>
     <row r="571" spans="1:5">
       <c r="A571" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B571" s="1" t="s">
         <v>117</v>
@@ -11669,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="D571" s="1">
-        <v>241.05</v>
+        <v>141.94999999999999</v>
       </c>
       <c r="E571" s="2">
         <v>45873</v>
@@ -11677,7 +11680,7 @@
     </row>
     <row r="572" spans="1:5">
       <c r="A572" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B572" s="1" t="s">
         <v>117</v>
@@ -11686,7 +11689,7 @@
         <v>1</v>
       </c>
       <c r="D572" s="1">
-        <v>234.85</v>
+        <v>241.05</v>
       </c>
       <c r="E572" s="2">
         <v>45873</v>
@@ -11694,7 +11697,7 @@
     </row>
     <row r="573" spans="1:5">
       <c r="A573" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="B573" s="1" t="s">
         <v>117</v>
@@ -11703,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="D573" s="1">
-        <v>374.75</v>
+        <v>234.85</v>
       </c>
       <c r="E573" s="2">
         <v>45873</v>
@@ -11711,7 +11714,7 @@
     </row>
     <row r="574" spans="1:5">
       <c r="A574" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="B574" s="1" t="s">
         <v>117</v>
@@ -11720,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="D574" s="1">
-        <v>1990.3</v>
+        <v>374.75</v>
       </c>
       <c r="E574" s="2">
         <v>45873</v>
@@ -11728,7 +11731,7 @@
     </row>
     <row r="575" spans="1:5">
       <c r="A575" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="B575" s="1" t="s">
         <v>117</v>
@@ -11737,7 +11740,7 @@
         <v>1</v>
       </c>
       <c r="D575" s="1">
-        <v>2663.5</v>
+        <v>1990.3</v>
       </c>
       <c r="E575" s="2">
         <v>45873</v>
@@ -11745,16 +11748,16 @@
     </row>
     <row r="576" spans="1:5">
       <c r="A576" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="B576" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C576" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D576" s="1">
-        <v>1645.4</v>
+        <v>2663.5</v>
       </c>
       <c r="E576" s="2">
         <v>45873</v>
@@ -11762,16 +11765,16 @@
     </row>
     <row r="577" spans="1:5">
       <c r="A577" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="B577" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C577" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D577" s="1">
-        <v>958.8</v>
+        <v>1645.4</v>
       </c>
       <c r="E577" s="2">
         <v>45873</v>
@@ -11785,7 +11788,7 @@
         <v>117</v>
       </c>
       <c r="C578" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D578" s="1">
         <v>958.8</v>
@@ -11802,7 +11805,7 @@
         <v>117</v>
       </c>
       <c r="C579" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D579" s="1">
         <v>958.8</v>
@@ -11836,7 +11839,7 @@
         <v>117</v>
       </c>
       <c r="C581" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D581" s="1">
         <v>958.8</v>
@@ -11847,7 +11850,7 @@
     </row>
     <row r="582" spans="1:5">
       <c r="A582" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="B582" s="1" t="s">
         <v>117</v>
@@ -11856,7 +11859,7 @@
         <v>1</v>
       </c>
       <c r="D582" s="1">
-        <v>5250.35</v>
+        <v>958.8</v>
       </c>
       <c r="E582" s="2">
         <v>45873</v>
@@ -11873,7 +11876,7 @@
         <v>1</v>
       </c>
       <c r="D583" s="1">
-        <v>5250.25</v>
+        <v>5250.35</v>
       </c>
       <c r="E583" s="2">
         <v>45873</v>
@@ -11881,16 +11884,16 @@
     </row>
     <row r="584" spans="1:5">
       <c r="A584" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B584" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C584" s="1">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D584" s="1">
-        <v>137.19999999999999</v>
+        <v>5250.25</v>
       </c>
       <c r="E584" s="2">
         <v>45873</v>
@@ -11904,10 +11907,10 @@
         <v>117</v>
       </c>
       <c r="C585" s="1">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D585" s="1">
-        <v>137</v>
+        <v>137.19999999999999</v>
       </c>
       <c r="E585" s="2">
         <v>45873</v>
@@ -11921,10 +11924,10 @@
         <v>117</v>
       </c>
       <c r="C586" s="1">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D586" s="1">
-        <v>137.32</v>
+        <v>137</v>
       </c>
       <c r="E586" s="2">
         <v>45873</v>
@@ -11938,10 +11941,10 @@
         <v>117</v>
       </c>
       <c r="C587" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D587" s="1">
-        <v>137</v>
+        <v>137.32</v>
       </c>
       <c r="E587" s="2">
         <v>45873</v>
@@ -11975,7 +11978,7 @@
         <v>10</v>
       </c>
       <c r="D589" s="1">
-        <v>137.02000000000001</v>
+        <v>137</v>
       </c>
       <c r="E589" s="2">
         <v>45873</v>
@@ -11989,10 +11992,10 @@
         <v>117</v>
       </c>
       <c r="C590" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D590" s="1">
-        <v>137.01</v>
+        <v>137.02000000000001</v>
       </c>
       <c r="E590" s="2">
         <v>45873</v>
@@ -12009,7 +12012,7 @@
         <v>1</v>
       </c>
       <c r="D591" s="1">
-        <v>137.04</v>
+        <v>137.01</v>
       </c>
       <c r="E591" s="2">
         <v>45873</v>
@@ -12026,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="D592" s="1">
-        <v>137.06</v>
+        <v>137.04</v>
       </c>
       <c r="E592" s="2">
         <v>45873</v>
@@ -12043,7 +12046,7 @@
         <v>1</v>
       </c>
       <c r="D593" s="1">
-        <v>137.12</v>
+        <v>137.06</v>
       </c>
       <c r="E593" s="2">
         <v>45873</v>
@@ -12060,7 +12063,7 @@
         <v>1</v>
       </c>
       <c r="D594" s="1">
-        <v>137.21</v>
+        <v>137.12</v>
       </c>
       <c r="E594" s="2">
         <v>45873</v>
@@ -12077,7 +12080,7 @@
         <v>1</v>
       </c>
       <c r="D595" s="1">
-        <v>137.30000000000001</v>
+        <v>137.21</v>
       </c>
       <c r="E595" s="2">
         <v>45873</v>
@@ -12094,7 +12097,7 @@
         <v>1</v>
       </c>
       <c r="D596" s="1">
-        <v>137.26</v>
+        <v>137.30000000000001</v>
       </c>
       <c r="E596" s="2">
         <v>45873</v>
@@ -12108,10 +12111,10 @@
         <v>117</v>
       </c>
       <c r="C597" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D597" s="1">
-        <v>137.63</v>
+        <v>137.26</v>
       </c>
       <c r="E597" s="2">
         <v>45873</v>
@@ -12125,10 +12128,10 @@
         <v>117</v>
       </c>
       <c r="C598" s="1">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D598" s="1">
-        <v>137.03</v>
+        <v>137.63</v>
       </c>
       <c r="E598" s="2">
         <v>45873</v>
@@ -12136,16 +12139,16 @@
     </row>
     <row r="599" spans="1:5">
       <c r="A599" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="B599" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C599" s="1">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D599" s="1">
-        <v>982.9</v>
+        <v>137.03</v>
       </c>
       <c r="E599" s="2">
         <v>45873</v>
@@ -12153,19 +12156,19 @@
     </row>
     <row r="600" spans="1:5">
       <c r="A600" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C600" s="1">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D600" s="1">
-        <v>168.16</v>
+        <v>982.9</v>
       </c>
       <c r="E600" s="2">
-        <v>45876</v>
+        <v>45873</v>
       </c>
     </row>
     <row r="601" spans="1:5">
@@ -12176,10 +12179,10 @@
         <v>113</v>
       </c>
       <c r="C601" s="1">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D601" s="1">
-        <v>168.13</v>
+        <v>168.16</v>
       </c>
       <c r="E601" s="2">
         <v>45876</v>
@@ -12193,10 +12196,10 @@
         <v>113</v>
       </c>
       <c r="C602" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D602" s="1">
-        <v>168.15</v>
+        <v>168.13</v>
       </c>
       <c r="E602" s="2">
         <v>45876</v>
@@ -12210,7 +12213,7 @@
         <v>113</v>
       </c>
       <c r="C603" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D603" s="1">
         <v>168.15</v>
@@ -12221,16 +12224,16 @@
     </row>
     <row r="604" spans="1:5">
       <c r="A604" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="B604" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C604" s="1">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="D604" s="1">
-        <v>45.02</v>
+        <v>168.15</v>
       </c>
       <c r="E604" s="2">
         <v>45876</v>
@@ -12238,19 +12241,19 @@
     </row>
     <row r="605" spans="1:5">
       <c r="A605" t="s">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="B605" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C605" s="1">
-        <v>129</v>
+        <v>500</v>
       </c>
       <c r="D605" s="1">
-        <v>72.98</v>
+        <v>45.02</v>
       </c>
       <c r="E605" s="2">
-        <v>45880</v>
+        <v>45876</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -12261,7 +12264,7 @@
         <v>113</v>
       </c>
       <c r="C606" s="1">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="D606" s="1">
         <v>72.98</v>
@@ -12272,7 +12275,7 @@
     </row>
     <row r="607" spans="1:5">
       <c r="A607" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="B607" s="1" t="s">
         <v>113</v>
@@ -12281,7 +12284,7 @@
         <v>1</v>
       </c>
       <c r="D607" s="1">
-        <v>712.2</v>
+        <v>72.98</v>
       </c>
       <c r="E607" s="2">
         <v>45880</v>
@@ -12295,7 +12298,7 @@
         <v>113</v>
       </c>
       <c r="C608" s="1">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D608" s="1">
         <v>712.2</v>
@@ -12306,53 +12309,53 @@
     </row>
     <row r="609" spans="1:5">
       <c r="A609" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="B609" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C609" s="1">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="D609" s="1">
-        <v>219.13</v>
+        <v>712.2</v>
       </c>
       <c r="E609" s="2">
-        <v>45895</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="610" spans="1:5">
       <c r="A610" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B610" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C610" s="1">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="D610" s="1">
-        <v>4.13</v>
+        <v>219.13</v>
       </c>
       <c r="E610" s="2">
-        <v>45904</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="611" spans="1:5">
       <c r="A611" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="B611" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C611" s="1">
-        <v>98</v>
+        <v>1900</v>
       </c>
       <c r="D611" s="1">
-        <v>248.01</v>
+        <v>4.13</v>
       </c>
       <c r="E611" s="2">
-        <v>45908</v>
+        <v>45904</v>
       </c>
     </row>
     <row r="612" spans="1:5">
@@ -12363,7 +12366,7 @@
         <v>113</v>
       </c>
       <c r="C612" s="1">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="D612" s="1">
         <v>248.01</v>
@@ -12374,16 +12377,16 @@
     </row>
     <row r="613" spans="1:5">
       <c r="A613" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="B613" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C613" s="1">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="D613" s="1">
-        <v>3.91</v>
+        <v>248.01</v>
       </c>
       <c r="E613" s="2">
         <v>45908</v>
@@ -12400,7 +12403,7 @@
         <v>300</v>
       </c>
       <c r="D614" s="1">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="E614" s="2">
         <v>45908</v>
@@ -12408,67 +12411,67 @@
     </row>
     <row r="615" spans="1:5">
       <c r="A615" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="B615" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C615" s="1">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D615" s="1">
-        <v>86.18</v>
+        <v>3.9</v>
       </c>
       <c r="E615" s="2">
-        <v>45915</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="616" spans="1:5">
       <c r="A616" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="B616" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C616" s="1">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="D616" s="1">
-        <v>9.66</v>
+        <v>86.18</v>
       </c>
       <c r="E616" s="2">
-        <v>45930</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="617" spans="1:5">
       <c r="A617" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="B617" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C617" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D617" s="1">
-        <v>123</v>
+        <v>9.66</v>
       </c>
       <c r="E617" s="2">
-        <v>45951</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="618" spans="1:5">
       <c r="A618" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="B618" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C618" s="1">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="D618" s="1">
-        <v>8.09</v>
+        <v>123</v>
       </c>
       <c r="E618" s="2">
         <v>45951</v>
@@ -12476,16 +12479,16 @@
     </row>
     <row r="619" spans="1:5">
       <c r="A619" t="s">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="B619" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C619" s="1">
-        <v>60</v>
+        <v>1500</v>
       </c>
       <c r="D619" s="1">
-        <v>485.45</v>
+        <v>8.09</v>
       </c>
       <c r="E619" s="2">
         <v>45951</v>
@@ -12493,16 +12496,16 @@
     </row>
     <row r="620" spans="1:5">
       <c r="A620" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B620" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C620" s="1">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="D620" s="1">
-        <v>43.34</v>
+        <v>485.45</v>
       </c>
       <c r="E620" s="2">
         <v>45951</v>
@@ -12510,16 +12513,16 @@
     </row>
     <row r="621" spans="1:5">
       <c r="A621" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B621" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C621" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D621" s="1">
-        <v>10.17</v>
+        <v>43.34</v>
       </c>
       <c r="E621" s="2">
         <v>45951</v>
@@ -12527,16 +12530,16 @@
     </row>
     <row r="622" spans="1:5">
       <c r="A622" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="B622" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C622" s="1">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="D622" s="1">
-        <v>534.75</v>
+        <v>10.17</v>
       </c>
       <c r="E622" s="2">
         <v>45951</v>
@@ -12550,12 +12553,29 @@
         <v>113</v>
       </c>
       <c r="C623" s="1">
+        <v>6</v>
+      </c>
+      <c r="D623" s="1">
+        <v>534.75</v>
+      </c>
+      <c r="E623" s="2">
+        <v>45951</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5">
+      <c r="A624" t="s">
+        <v>146</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C624" s="1">
         <v>19</v>
       </c>
-      <c r="D623" s="1">
+      <c r="D624" s="1">
         <v>534.70000000000005</v>
       </c>
-      <c r="E623" s="2">
+      <c r="E624" s="2">
         <v>45951</v>
       </c>
     </row>
